--- a/gstdatabase/GSTR-3B-2025-2026.xlsx
+++ b/gstdatabase/GSTR-3B-2025-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5B3360-1307-40A2-8D87-E681E0F0D192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6862F1-96AC-4E06-BF00-24D2F5EFD188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>FINANCIAL YEAR 2025-2026</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -1293,14 +1293,14 @@
       </c>
       <c r="E10" s="4">
         <f>F10-D10</f>
-        <v>15071</v>
+        <v>15099</v>
       </c>
       <c r="F10" s="13">
-        <v>74303</v>
+        <v>74331</v>
       </c>
       <c r="G10" s="5">
         <f>F10/C10</f>
-        <v>1.0015366159403685</v>
+        <v>1.0019140303818626</v>
       </c>
       <c r="H10" s="7">
         <v>75899</v>
@@ -1310,14 +1310,14 @@
       </c>
       <c r="J10" s="4">
         <f>K10-I10</f>
-        <v>14934</v>
+        <v>14969</v>
       </c>
       <c r="K10" s="13">
-        <v>75018</v>
+        <v>75053</v>
       </c>
       <c r="L10" s="5">
         <f>K10/H10</f>
-        <v>0.98839246893898469</v>
+        <v>0.98885360808442802</v>
       </c>
       <c r="M10" s="7">
         <v>134494</v>
@@ -1327,14 +1327,14 @@
       </c>
       <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>26306</v>
+        <v>26371</v>
       </c>
       <c r="P10" s="13">
-        <v>134142</v>
+        <v>134207</v>
       </c>
       <c r="Q10" s="5">
         <f>P10/M10</f>
-        <v>0.99738278287507254</v>
+        <v>0.99786607581007336</v>
       </c>
       <c r="R10" s="7">
         <v>73914</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="T10" s="4">
         <f>U10-S10</f>
-        <v>13970</v>
+        <v>14009</v>
       </c>
       <c r="U10" s="13">
-        <v>73826</v>
+        <v>73865</v>
       </c>
       <c r="V10" s="5">
         <f>U10/R10</f>
-        <v>0.99880942717211896</v>
+        <v>0.99933706740265715</v>
       </c>
       <c r="W10" s="7">
         <v>75592</v>
@@ -1361,14 +1361,14 @@
       </c>
       <c r="Y10" s="4">
         <f>Z10-X10</f>
-        <v>14060</v>
+        <v>14105</v>
       </c>
       <c r="Z10" s="13">
-        <v>74743</v>
+        <v>74788</v>
       </c>
       <c r="AA10" s="5">
         <f>Z10/W10</f>
-        <v>0.9887686527674886</v>
+        <v>0.98936395385755105</v>
       </c>
       <c r="AB10" s="7">
         <v>136558</v>
@@ -1378,14 +1378,14 @@
       </c>
       <c r="AD10" s="4">
         <f>AE10-AC10</f>
-        <v>24173</v>
+        <v>24273</v>
       </c>
       <c r="AE10" s="13">
-        <v>136025</v>
+        <v>136125</v>
       </c>
       <c r="AF10" s="5">
         <f>AE10/AB10</f>
-        <v>0.99609689655677436</v>
+        <v>0.99682918613336458</v>
       </c>
       <c r="AG10" s="7">
         <v>73704</v>
@@ -1395,14 +1395,14 @@
       </c>
       <c r="AI10" s="4">
         <f>AJ10-AH10</f>
-        <v>14148</v>
+        <v>14219</v>
       </c>
       <c r="AJ10" s="13">
-        <v>73560</v>
+        <v>73631</v>
       </c>
       <c r="AK10" s="5">
         <f>AJ10/AG10</f>
-        <v>0.99804623901009448</v>
+        <v>0.99900955172039507</v>
       </c>
       <c r="AL10" s="7">
         <v>75897</v>
@@ -1412,14 +1412,14 @@
       </c>
       <c r="AN10" s="4">
         <f>AO10-AM10</f>
-        <v>12968</v>
+        <v>13063</v>
       </c>
       <c r="AO10" s="13">
-        <v>76163</v>
+        <v>76258</v>
       </c>
       <c r="AP10" s="5">
         <f>AO10/AL10</f>
-        <v>1.0035047498583607</v>
+        <v>1.0047564462363465</v>
       </c>
       <c r="AQ10" s="7">
         <v>140117</v>
@@ -1429,14 +1429,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>25307</v>
+        <v>25553</v>
       </c>
       <c r="AT10" s="13">
-        <v>140265</v>
+        <v>140511</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>1.0010562601254667</v>
+        <v>1.0028119357394178</v>
       </c>
       <c r="AV10" s="7">
         <v>75508</v>
@@ -1446,14 +1446,14 @@
       </c>
       <c r="AX10" s="4">
         <f>AY10-AW10</f>
-        <v>13617</v>
+        <v>13800</v>
       </c>
       <c r="AY10" s="13">
-        <v>76013</v>
+        <v>76196</v>
       </c>
       <c r="AZ10" s="5">
         <f>AY10/AV10</f>
-        <v>1.0066880330561001</v>
+        <v>1.0091116173120729</v>
       </c>
       <c r="BA10" s="7">
         <v>78056</v>
@@ -1463,14 +1463,14 @@
       </c>
       <c r="BC10" s="4">
         <f>BD10-BB10</f>
-        <v>13576</v>
+        <v>13840</v>
       </c>
       <c r="BD10" s="13">
-        <v>77572</v>
+        <v>77836</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10/BA10</f>
-        <v>0.9937993235625705</v>
+        <v>0.99718151071025929</v>
       </c>
       <c r="BF10" s="7">
         <v>144885</v>
@@ -1480,14 +1480,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>32461</v>
+        <v>33364</v>
       </c>
       <c r="BI10" s="6">
-        <v>142503</v>
+        <v>143406</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.98355937467646759</v>
+        <v>0.98979190392380167</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1505,14 +1505,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>8654</v>
+        <v>8662</v>
       </c>
       <c r="F11" s="13">
-        <v>47800</v>
+        <v>47808</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99926831817706696</v>
+        <v>0.99943555973659459</v>
       </c>
       <c r="H11" s="7">
         <v>49123</v>
@@ -1522,14 +1522,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>8333</v>
+        <v>8341</v>
       </c>
       <c r="K11" s="13">
-        <v>48319</v>
+        <v>48327</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98363292144209435</v>
+        <v>0.98379577794515805</v>
       </c>
       <c r="M11" s="7">
         <v>111861</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>19051</v>
+        <v>19090</v>
       </c>
       <c r="P11" s="13">
-        <v>111240</v>
+        <v>111279</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.9944484672942312</v>
+        <v>0.9947971142757529</v>
       </c>
       <c r="R11" s="7">
         <v>47958</v>
@@ -1556,14 +1556,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>8122</v>
+        <v>8139</v>
       </c>
       <c r="U11" s="13">
-        <v>47716</v>
+        <v>47733</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.9949539180115935</v>
+        <v>0.99530839484548983</v>
       </c>
       <c r="W11" s="7">
         <v>49731</v>
@@ -1573,14 +1573,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8144</v>
+        <v>8162</v>
       </c>
       <c r="Z11" s="13">
-        <v>48346</v>
+        <v>48364</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.97215016790331987</v>
+        <v>0.97251211517966663</v>
       </c>
       <c r="AB11" s="7">
         <v>113134</v>
@@ -1590,14 +1590,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>19630</v>
+        <v>19694</v>
       </c>
       <c r="AE11" s="13">
-        <v>112010</v>
+        <v>112074</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.99006487881627092</v>
+        <v>0.99063057966659007</v>
       </c>
       <c r="AG11" s="7">
         <v>48119</v>
@@ -1607,14 +1607,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>7904</v>
+        <v>7942</v>
       </c>
       <c r="AJ11" s="13">
-        <v>47776</v>
+        <v>47814</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99287183856688621</v>
+        <v>0.99366154741370349</v>
       </c>
       <c r="AL11" s="7">
         <v>49938</v>
@@ -1624,14 +1624,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>7403</v>
+        <v>7454</v>
       </c>
       <c r="AO11" s="13">
-        <v>49089</v>
+        <v>49140</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.98299891865913736</v>
+        <v>0.98402018502943656</v>
       </c>
       <c r="AQ11" s="7">
         <v>114343</v>
@@ -1641,14 +1641,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>16008</v>
+        <v>16155</v>
       </c>
       <c r="AT11" s="13">
-        <v>113747</v>
+        <v>113894</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.99478761270912952</v>
+        <v>0.99607321829932749</v>
       </c>
       <c r="AV11" s="7">
         <v>49251</v>
@@ -1658,14 +1658,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>7055</v>
+        <v>7144</v>
       </c>
       <c r="AY11" s="13">
-        <v>48818</v>
+        <v>48907</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.99120830033907936</v>
+        <v>0.99301537024628939</v>
       </c>
       <c r="BA11" s="7">
         <v>50523</v>
@@ -1675,14 +1675,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>7342</v>
+        <v>7482</v>
       </c>
       <c r="BD11" s="13">
-        <v>49541</v>
+        <v>49681</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.98056330780040768</v>
+        <v>0.98333432298161239</v>
       </c>
       <c r="BF11" s="7">
         <v>116408</v>
@@ -1692,14 +1692,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>18510</v>
+        <v>19198</v>
       </c>
       <c r="BI11" s="6">
-        <v>113967</v>
+        <v>114655</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.97903065081437701</v>
+        <v>0.98494089753281566</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>29293</v>
+        <v>29312</v>
       </c>
       <c r="F12" s="13">
-        <v>182266</v>
+        <v>182285</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.99736248823516538</v>
+        <v>0.9974664565412481</v>
       </c>
       <c r="H12" s="7">
         <v>186824</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>26580</v>
+        <v>26605</v>
       </c>
       <c r="K12" s="13">
-        <v>184695</v>
+        <v>184720</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
-        <v>0.98860424784824219</v>
+        <v>0.9887380636320815</v>
       </c>
       <c r="M12" s="7">
         <v>372375</v>
@@ -1751,14 +1751,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>61090</v>
+        <v>61149</v>
       </c>
       <c r="P12" s="13">
-        <v>370704</v>
+        <v>370763</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.99551258811681775</v>
+        <v>0.99567103054716344</v>
       </c>
       <c r="R12" s="7">
         <v>184659</v>
@@ -1768,14 +1768,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>28372</v>
+        <v>28412</v>
       </c>
       <c r="U12" s="13">
-        <v>183716</v>
+        <v>183756</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.99489328979361957</v>
+        <v>0.99510990528487642</v>
       </c>
       <c r="W12" s="7">
         <v>189081</v>
@@ -1785,14 +1785,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>29799</v>
+        <v>29845</v>
       </c>
       <c r="Z12" s="13">
-        <v>185716</v>
+        <v>185762</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.98220339431249037</v>
+        <v>0.98244667629217108</v>
       </c>
       <c r="AB12" s="7">
         <v>377441</v>
@@ -1802,14 +1802,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>65561</v>
+        <v>65685</v>
       </c>
       <c r="AE12" s="13">
-        <v>374182</v>
+        <v>374306</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.99136553792513271</v>
+        <v>0.99169406609244892</v>
       </c>
       <c r="AG12" s="7">
         <v>186148</v>
@@ -1819,14 +1819,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>28607</v>
+        <v>28688</v>
       </c>
       <c r="AJ12" s="13">
-        <v>185048</v>
+        <v>185129</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.99409072351032512</v>
+        <v>0.99452586114274666</v>
       </c>
       <c r="AL12" s="7">
         <v>192239</v>
@@ -1836,14 +1836,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>26924</v>
+        <v>27046</v>
       </c>
       <c r="AO12" s="13">
-        <v>191177</v>
+        <v>191299</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.99447562669385503</v>
+        <v>0.99511025338250825</v>
       </c>
       <c r="AQ12" s="7">
         <v>384779</v>
@@ -1853,14 +1853,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>61162</v>
+        <v>61534</v>
       </c>
       <c r="AT12" s="13">
-        <v>383364</v>
+        <v>383736</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.99632256438111233</v>
+        <v>0.99728935310918732</v>
       </c>
       <c r="AV12" s="7">
         <v>191743</v>
@@ -1870,14 +1870,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>25858</v>
+        <v>26184</v>
       </c>
       <c r="AY12" s="13">
-        <v>191363</v>
+        <v>191689</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.9980181805854712</v>
+        <v>0.99971837303056699</v>
       </c>
       <c r="BA12" s="7">
         <v>197493</v>
@@ -1887,14 +1887,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>27188</v>
+        <v>27664</v>
       </c>
       <c r="BD12" s="13">
-        <v>194495</v>
+        <v>194971</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.98481971512914379</v>
+        <v>0.98722992713665803</v>
       </c>
       <c r="BF12" s="7">
         <v>393305</v>
@@ -1904,14 +1904,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>70907</v>
+        <v>72959</v>
       </c>
       <c r="BI12" s="6">
-        <v>386886</v>
+        <v>388938</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.98367933283329734</v>
+        <v>0.9888966578100965</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1929,14 +1929,14 @@
       </c>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
-        <v>2893</v>
+        <v>2896</v>
       </c>
       <c r="F13" s="13">
-        <v>18070</v>
+        <v>18073</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>1.0019406709176601</v>
+        <v>1.0021070141391739</v>
       </c>
       <c r="H13" s="7">
         <v>18257</v>
@@ -1946,14 +1946,14 @@
       </c>
       <c r="J13" s="4">
         <f t="shared" si="2"/>
-        <v>2625</v>
+        <v>2628</v>
       </c>
       <c r="K13" s="13">
-        <v>18103</v>
+        <v>18106</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="3"/>
-        <v>0.99156487922440706</v>
+        <v>0.99172919975899654</v>
       </c>
       <c r="M13" s="7">
         <v>29011</v>
@@ -1963,14 +1963,14 @@
       </c>
       <c r="O13" s="4">
         <f t="shared" si="4"/>
-        <v>5012</v>
+        <v>5017</v>
       </c>
       <c r="P13" s="13">
-        <v>29006</v>
+        <v>29011</v>
       </c>
       <c r="Q13" s="5">
         <f t="shared" si="5"/>
-        <v>0.99982765158043496</v>
+        <v>1</v>
       </c>
       <c r="R13" s="7">
         <v>18140</v>
@@ -1980,14 +1980,14 @@
       </c>
       <c r="T13" s="4">
         <f t="shared" si="6"/>
-        <v>2802</v>
+        <v>2806</v>
       </c>
       <c r="U13" s="13">
-        <v>18169</v>
+        <v>18173</v>
       </c>
       <c r="V13" s="5">
         <f t="shared" si="7"/>
-        <v>1.0015986769570011</v>
+        <v>1.001819184123484</v>
       </c>
       <c r="W13" s="7">
         <v>18401</v>
@@ -1997,14 +1997,14 @@
       </c>
       <c r="Y13" s="4">
         <f t="shared" si="8"/>
-        <v>2812</v>
+        <v>2817</v>
       </c>
       <c r="Z13" s="13">
-        <v>18243</v>
+        <v>18248</v>
       </c>
       <c r="AA13" s="5">
         <f t="shared" si="9"/>
-        <v>0.99141351013531875</v>
+        <v>0.99168523449812507</v>
       </c>
       <c r="AB13" s="7">
         <v>29242</v>
@@ -2014,14 +2014,14 @@
       </c>
       <c r="AD13" s="4">
         <f t="shared" si="10"/>
-        <v>4843</v>
+        <v>4854</v>
       </c>
       <c r="AE13" s="13">
-        <v>29206</v>
+        <v>29217</v>
       </c>
       <c r="AF13" s="5">
         <f t="shared" si="11"/>
-        <v>0.99876889405649405</v>
+        <v>0.99914506531700975</v>
       </c>
       <c r="AG13" s="7">
         <v>18261</v>
@@ -2031,14 +2031,14 @@
       </c>
       <c r="AI13" s="4">
         <f t="shared" si="12"/>
-        <v>2713</v>
+        <v>2722</v>
       </c>
       <c r="AJ13" s="13">
-        <v>18420</v>
+        <v>18429</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="13"/>
-        <v>1.0087070806637095</v>
+        <v>1.0091999342861837</v>
       </c>
       <c r="AL13" s="7">
         <v>18637</v>
@@ -2048,14 +2048,14 @@
       </c>
       <c r="AN13" s="4">
         <f t="shared" si="14"/>
-        <v>2573</v>
+        <v>2588</v>
       </c>
       <c r="AO13" s="13">
-        <v>18735</v>
+        <v>18750</v>
       </c>
       <c r="AP13" s="5">
         <f t="shared" si="15"/>
-        <v>1.0052583570317111</v>
+        <v>1.0060632075977893</v>
       </c>
       <c r="AQ13" s="7">
         <v>29668</v>
@@ -2065,14 +2065,14 @@
       </c>
       <c r="AS13" s="4">
         <f t="shared" si="16"/>
-        <v>4318</v>
+        <v>4352</v>
       </c>
       <c r="AT13" s="13">
-        <v>29794</v>
+        <v>29828</v>
       </c>
       <c r="AU13" s="5">
         <f t="shared" si="17"/>
-        <v>1.0042470001348254</v>
+        <v>1.0053930160442228</v>
       </c>
       <c r="AV13" s="7">
         <v>18676</v>
@@ -2082,14 +2082,14 @@
       </c>
       <c r="AX13" s="4">
         <f t="shared" si="18"/>
-        <v>2502</v>
+        <v>2539</v>
       </c>
       <c r="AY13" s="13">
-        <v>18873</v>
+        <v>18910</v>
       </c>
       <c r="AZ13" s="5">
         <f t="shared" si="19"/>
-        <v>1.0105482972799316</v>
+        <v>1.0125294495609338</v>
       </c>
       <c r="BA13" s="7">
         <v>19025</v>
@@ -2099,14 +2099,14 @@
       </c>
       <c r="BC13" s="4">
         <f t="shared" si="20"/>
-        <v>2523</v>
+        <v>2580</v>
       </c>
       <c r="BD13" s="13">
-        <v>19110</v>
+        <v>19167</v>
       </c>
       <c r="BE13" s="5">
         <f t="shared" si="21"/>
-        <v>1.0044678055190539</v>
+        <v>1.0074638633377135</v>
       </c>
       <c r="BF13" s="7">
         <v>30254</v>
@@ -2116,14 +2116,14 @@
       </c>
       <c r="BH13" s="4">
         <f t="shared" si="22"/>
-        <v>4838</v>
+        <v>5016</v>
       </c>
       <c r="BI13" s="6">
-        <v>29963</v>
+        <v>30141</v>
       </c>
       <c r="BJ13" s="5">
         <f t="shared" si="23"/>
-        <v>0.99038143716533356</v>
+        <v>0.99626495669994053</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>19361</v>
+        <v>19393</v>
       </c>
       <c r="F14" s="13">
-        <v>95509</v>
+        <v>95541</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>1.0094701573779501</v>
+        <v>1.0098083772843056</v>
       </c>
       <c r="H14" s="7">
         <v>97351</v>
@@ -2158,14 +2158,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>18907</v>
+        <v>18943</v>
       </c>
       <c r="K14" s="13">
-        <v>97333</v>
+        <v>97369</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.99981510205339441</v>
+        <v>1.0001848979466055</v>
       </c>
       <c r="M14" s="7">
         <v>172809</v>
@@ -2175,14 +2175,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>35796</v>
+        <v>35867</v>
       </c>
       <c r="P14" s="13">
-        <v>172559</v>
+        <v>172630</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.99855331608886111</v>
+        <v>0.99896417431962459</v>
       </c>
       <c r="R14" s="7">
         <v>97326</v>
@@ -2192,14 +2192,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>17991</v>
+        <v>18039</v>
       </c>
       <c r="U14" s="13">
-        <v>96844</v>
+        <v>96892</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.99504757207734829</v>
+        <v>0.99554075992026791</v>
       </c>
       <c r="W14" s="7">
         <v>98912</v>
@@ -2209,14 +2209,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>17719</v>
+        <v>17771</v>
       </c>
       <c r="Z14" s="13">
-        <v>97998</v>
+        <v>98050</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.99075946295697181</v>
+        <v>0.99128518278874156</v>
       </c>
       <c r="AB14" s="7">
         <v>175426</v>
@@ -2226,14 +2226,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>34523</v>
+        <v>34644</v>
       </c>
       <c r="AE14" s="13">
-        <v>175231</v>
+        <v>175352</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.99888842018856949</v>
+        <v>0.9995781697125854</v>
       </c>
       <c r="AG14" s="7">
         <v>98057</v>
@@ -2243,14 +2243,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>18650</v>
+        <v>18735</v>
       </c>
       <c r="AJ14" s="13">
-        <v>98248</v>
+        <v>98333</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>1.0019478466606158</v>
+        <v>1.00281468941534</v>
       </c>
       <c r="AL14" s="7">
         <v>101581</v>
@@ -2260,14 +2260,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>17915</v>
+        <v>18044</v>
       </c>
       <c r="AO14" s="13">
-        <v>102594</v>
+        <v>102723</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>1.009972337346551</v>
+        <v>1.0112422598714326</v>
       </c>
       <c r="AQ14" s="7">
         <v>182247</v>
@@ -2277,14 +2277,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>31416</v>
+        <v>31695</v>
       </c>
       <c r="AT14" s="13">
-        <v>182310</v>
+        <v>182589</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>1.0003456847026289</v>
+        <v>1.0018765740999851</v>
       </c>
       <c r="AV14" s="7">
         <v>102257</v>
@@ -2294,14 +2294,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>17614</v>
+        <v>17856</v>
       </c>
       <c r="AY14" s="13">
-        <v>103122</v>
+        <v>103364</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>1.0084590785960863</v>
+        <v>1.0108256647466678</v>
       </c>
       <c r="BA14" s="7">
         <v>106311</v>
@@ -2311,14 +2311,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>17594</v>
+        <v>17918</v>
       </c>
       <c r="BD14" s="13">
-        <v>105504</v>
+        <v>105828</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.99240906397268391</v>
+        <v>0.99545672602082569</v>
       </c>
       <c r="BF14" s="7">
         <v>189210</v>
@@ -2328,14 +2328,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>38259</v>
+        <v>39468</v>
       </c>
       <c r="BI14" s="6">
-        <v>185898</v>
+        <v>187107</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.98249563976534005</v>
+        <v>0.9888853654669415</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2353,14 +2353,14 @@
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
-        <v>55227</v>
+        <v>55252</v>
       </c>
       <c r="F15" s="13">
-        <v>324400</v>
+        <v>324425</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.99878077316223102</v>
+        <v>0.9988577445535044</v>
       </c>
       <c r="H15" s="7">
         <v>331968</v>
@@ -2370,14 +2370,14 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" si="2"/>
-        <v>52221</v>
+        <v>52247</v>
       </c>
       <c r="K15" s="13">
-        <v>329584</v>
+        <v>329610</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="3"/>
-        <v>0.99281858492384811</v>
+        <v>0.9928969057258531</v>
       </c>
       <c r="M15" s="7">
         <v>549212</v>
@@ -2387,14 +2387,14 @@
       </c>
       <c r="O15" s="4">
         <f t="shared" si="4"/>
-        <v>93456</v>
+        <v>93523</v>
       </c>
       <c r="P15" s="13">
-        <v>547392</v>
+        <v>547459</v>
       </c>
       <c r="Q15" s="5">
         <f t="shared" si="5"/>
-        <v>0.9966861612637743</v>
+        <v>0.99680815422823976</v>
       </c>
       <c r="R15" s="7">
         <v>333160</v>
@@ -2404,14 +2404,14 @@
       </c>
       <c r="T15" s="4">
         <f t="shared" si="6"/>
-        <v>53963</v>
+        <v>54013</v>
       </c>
       <c r="U15" s="13">
-        <v>332295</v>
+        <v>332345</v>
       </c>
       <c r="V15" s="5">
         <f t="shared" si="7"/>
-        <v>0.99740364989794694</v>
+        <v>0.99755372793852803</v>
       </c>
       <c r="W15" s="7">
         <v>340519</v>
@@ -2421,14 +2421,14 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="8"/>
-        <v>54923</v>
+        <v>54980</v>
       </c>
       <c r="Z15" s="13">
-        <v>336818</v>
+        <v>336875</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="9"/>
-        <v>0.98913129663836674</v>
+        <v>0.98929868817892685</v>
       </c>
       <c r="AB15" s="7">
         <v>562036</v>
@@ -2438,14 +2438,14 @@
       </c>
       <c r="AD15" s="4">
         <f t="shared" si="10"/>
-        <v>95039</v>
+        <v>95164</v>
       </c>
       <c r="AE15" s="13">
-        <v>558453</v>
+        <v>558578</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="11"/>
-        <v>0.99362496352546814</v>
+        <v>0.99384736920766636</v>
       </c>
       <c r="AG15" s="7">
         <v>340264</v>
@@ -2455,14 +2455,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>56129</v>
+        <v>56240</v>
       </c>
       <c r="AJ15" s="13">
-        <v>339263</v>
+        <v>339374</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.99705816660005175</v>
+        <v>0.99738438389015593</v>
       </c>
       <c r="AL15" s="7">
         <v>350627</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>54607</v>
+        <v>54760</v>
       </c>
       <c r="AO15" s="13">
-        <v>352490</v>
+        <v>352643</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>1.005313338676143</v>
+        <v>1.0057496998234592</v>
       </c>
       <c r="AQ15" s="7">
         <v>580651</v>
@@ -2489,14 +2489,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>83145</v>
+        <v>83650</v>
       </c>
       <c r="AT15" s="13">
-        <v>581070</v>
+        <v>581575</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>1.0007216038549835</v>
+        <v>1.0015913173317534</v>
       </c>
       <c r="AV15" s="7">
         <v>355536</v>
@@ -2506,14 +2506,14 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>51608</v>
+        <v>52149</v>
       </c>
       <c r="AY15" s="13">
-        <v>356628</v>
+        <v>357169</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>1.003071418928041</v>
+        <v>1.0045930651185815</v>
       </c>
       <c r="BA15" s="7">
         <v>365201</v>
@@ -2523,14 +2523,14 @@
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="20"/>
-        <v>52185</v>
+        <v>53065</v>
       </c>
       <c r="BD15" s="13">
-        <v>363167</v>
+        <v>364047</v>
       </c>
       <c r="BE15" s="5">
         <f t="shared" si="21"/>
-        <v>0.99443046431964865</v>
+        <v>0.99684009627574954</v>
       </c>
       <c r="BF15" s="7">
         <v>600313</v>
@@ -2540,14 +2540,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>101035</v>
+        <v>104023</v>
       </c>
       <c r="BI15" s="6">
-        <v>592071</v>
+        <v>595059</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.9862704955581505</v>
+        <v>0.99124789901268173</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2565,14 +2565,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>77190</v>
+        <v>77279</v>
       </c>
       <c r="F16" s="13">
-        <v>451929</v>
+        <v>452018</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.99649628019174541</v>
+        <v>0.99669252378075401</v>
       </c>
       <c r="H16" s="7">
         <v>461360</v>
@@ -2582,14 +2582,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>74951</v>
+        <v>75037</v>
       </c>
       <c r="K16" s="13">
-        <v>458770</v>
+        <v>458856</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.99438616264955781</v>
+        <v>0.99457256805964978</v>
       </c>
       <c r="M16" s="7">
         <v>788355</v>
@@ -2599,14 +2599,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>134567</v>
+        <v>134772</v>
       </c>
       <c r="P16" s="13">
-        <v>787566</v>
+        <v>787771</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.99899918184066827</v>
+        <v>0.99925921697712328</v>
       </c>
       <c r="R16" s="7">
         <v>462019</v>
@@ -2616,14 +2616,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>78315</v>
+        <v>78442</v>
       </c>
       <c r="U16" s="13">
-        <v>462463</v>
+        <v>462590</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>1.0009609994394171</v>
+        <v>1.0012358799097008</v>
       </c>
       <c r="W16" s="7">
         <v>472236</v>
@@ -2633,14 +2633,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>79017</v>
+        <v>79173</v>
       </c>
       <c r="Z16" s="13">
-        <v>467096</v>
+        <v>467252</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.98911561168568263</v>
+        <v>0.98944595498860743</v>
       </c>
       <c r="AB16" s="7">
         <v>804216</v>
@@ -2650,14 +2650,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>133923</v>
+        <v>134283</v>
       </c>
       <c r="AE16" s="13">
-        <v>799984</v>
+        <v>800344</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.99473773215156125</v>
+        <v>0.99518537308384813</v>
       </c>
       <c r="AG16" s="7">
         <v>471201</v>
@@ -2667,14 +2667,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>79156</v>
+        <v>79391</v>
       </c>
       <c r="AJ16" s="13">
-        <v>469545</v>
+        <v>469780</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.99648557621906575</v>
+        <v>0.99698430181599784</v>
       </c>
       <c r="AL16" s="7">
         <v>484445</v>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>79189</v>
+        <v>79487</v>
       </c>
       <c r="AO16" s="13">
-        <v>489333</v>
+        <v>489631</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>1.0100898966858982</v>
+        <v>1.0107050335951449</v>
       </c>
       <c r="AQ16" s="7">
         <v>831010</v>
@@ -2701,14 +2701,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>129840</v>
+        <v>130787</v>
       </c>
       <c r="AT16" s="13">
-        <v>832022</v>
+        <v>832969</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>1.0012177952130541</v>
+        <v>1.0023573723541233</v>
       </c>
       <c r="AV16" s="7">
         <v>496237</v>
@@ -2718,14 +2718,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>73928</v>
+        <v>74826</v>
       </c>
       <c r="AY16" s="13">
-        <v>496796</v>
+        <v>497694</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>1.0011264778724682</v>
+        <v>1.0029360970665226</v>
       </c>
       <c r="BA16" s="7">
         <v>510690</v>
@@ -2735,14 +2735,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>75288</v>
+        <v>76746</v>
       </c>
       <c r="BD16" s="13">
-        <v>505189</v>
+        <v>506647</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98922829896806286</v>
+        <v>0.99208325990326818</v>
       </c>
       <c r="BF16" s="7">
         <v>859721</v>
@@ -2752,14 +2752,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>136081</v>
+        <v>140386</v>
       </c>
       <c r="BI16" s="6">
-        <v>845774</v>
+        <v>850079</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.98377729519227752</v>
+        <v>0.98878473365196384</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2777,14 +2777,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>58639</v>
+        <v>58693</v>
       </c>
       <c r="F17" s="13">
-        <v>341407</v>
+        <v>341461</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>0.99751065713392484</v>
+        <v>0.99766843238600011</v>
       </c>
       <c r="H17" s="7">
         <v>352243</v>
@@ -2794,14 +2794,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>55193</v>
+        <v>55262</v>
       </c>
       <c r="K17" s="13">
-        <v>348412</v>
+        <v>348481</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.9891239854305125</v>
+        <v>0.98931987292863166</v>
       </c>
       <c r="M17" s="7">
         <v>765449</v>
@@ -2811,14 +2811,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>133412</v>
+        <v>133595</v>
       </c>
       <c r="P17" s="13">
-        <v>764166</v>
+        <v>764349</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.99832385959090675</v>
+        <v>0.99856293495712978</v>
       </c>
       <c r="R17" s="7">
         <v>346814</v>
@@ -2828,14 +2828,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>57041</v>
+        <v>57134</v>
       </c>
       <c r="U17" s="13">
-        <v>348508</v>
+        <v>348601</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>1.0048844625649485</v>
+        <v>1.0051526178297301</v>
       </c>
       <c r="W17" s="7">
         <v>360071</v>
@@ -2845,14 +2845,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>59410</v>
+        <v>59528</v>
       </c>
       <c r="Z17" s="13">
-        <v>356615</v>
+        <v>356733</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.99040189295999959</v>
+        <v>0.99072960610546257</v>
       </c>
       <c r="AB17" s="7">
         <v>784641</v>
@@ -2862,14 +2862,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>145791</v>
+        <v>146127</v>
       </c>
       <c r="AE17" s="13">
-        <v>782669</v>
+        <v>783005</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.99748674871692911</v>
+        <v>0.99791497003088037</v>
       </c>
       <c r="AG17" s="7">
         <v>355351</v>
@@ -2879,14 +2879,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>60212</v>
+        <v>60390</v>
       </c>
       <c r="AJ17" s="13">
-        <v>356779</v>
+        <v>356957</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>1.0040185619289097</v>
+        <v>1.0045194751105244</v>
       </c>
       <c r="AL17" s="7">
         <v>371770</v>
@@ -2896,14 +2896,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>55782</v>
+        <v>56055</v>
       </c>
       <c r="AO17" s="13">
-        <v>372739</v>
+        <v>373012</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>1.0026064502246013</v>
+        <v>1.0033407752104797</v>
       </c>
       <c r="AQ17" s="7">
         <v>810773</v>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>124519</v>
+        <v>125497</v>
       </c>
       <c r="AT17" s="13">
-        <v>811174</v>
+        <v>812152</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>1.0004945897310344</v>
+        <v>1.0017008459827843</v>
       </c>
       <c r="AV17" s="7">
         <v>369648</v>
@@ -2930,14 +2930,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>54578</v>
+        <v>55230</v>
       </c>
       <c r="AY17" s="13">
-        <v>372009</v>
+        <v>372661</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>1.0063871575120114</v>
+        <v>1.0081509977059255</v>
       </c>
       <c r="BA17" s="7">
         <v>385393</v>
@@ -2947,14 +2947,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>56043</v>
+        <v>57007</v>
       </c>
       <c r="BD17" s="13">
-        <v>382992</v>
+        <v>383956</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.99376999582244618</v>
+        <v>0.9962713386076032</v>
       </c>
       <c r="BF17" s="7">
         <v>839843</v>
@@ -2964,14 +2964,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>150382</v>
+        <v>155487</v>
       </c>
       <c r="BI17" s="6">
-        <v>825814</v>
+        <v>830919</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.9832956874082418</v>
+        <v>0.98937420446440583</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2989,14 +2989,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>190670</v>
+        <v>190835</v>
       </c>
       <c r="F18" s="13">
-        <v>1064206</v>
+        <v>1064371</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.99379001471719819</v>
+        <v>0.9939440970588016</v>
       </c>
       <c r="H18" s="7">
         <v>1089051</v>
@@ -3006,14 +3006,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>195301</v>
+        <v>195494</v>
       </c>
       <c r="K18" s="13">
-        <v>1079859</v>
+        <v>1080052</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.99155962392945785</v>
+        <v>0.99173684244355864</v>
       </c>
       <c r="M18" s="7">
         <v>1637429</v>
@@ -3023,14 +3023,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>300432</v>
+        <v>300786</v>
       </c>
       <c r="P18" s="13">
-        <v>1624469</v>
+        <v>1624823</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.99208515300510736</v>
+        <v>0.99230134558506045</v>
       </c>
       <c r="R18" s="7">
         <v>1090030</v>
@@ -3040,14 +3040,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>190916</v>
+        <v>191191</v>
       </c>
       <c r="U18" s="13">
-        <v>1079642</v>
+        <v>1079917</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.99046998706457623</v>
+        <v>0.99072227369888899</v>
       </c>
       <c r="W18" s="7">
         <v>1107435</v>
@@ -3057,14 +3057,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>193828</v>
+        <v>194191</v>
       </c>
       <c r="Z18" s="13">
-        <v>1090090</v>
+        <v>1090453</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.98433768121831078</v>
+        <v>0.98466546569324609</v>
       </c>
       <c r="AB18" s="7">
         <v>1665905</v>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>302402</v>
+        <v>303167</v>
       </c>
       <c r="AE18" s="13">
-        <v>1648047</v>
+        <v>1648812</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.98928030109760157</v>
+        <v>0.98973951095650714</v>
       </c>
       <c r="AG18" s="7">
         <v>1104366</v>
@@ -3091,14 +3091,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>202830</v>
+        <v>203447</v>
       </c>
       <c r="AJ18" s="13">
-        <v>1095184</v>
+        <v>1095801</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.99168572737661242</v>
+        <v>0.99224441896979809</v>
       </c>
       <c r="AL18" s="7">
         <v>1131950</v>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>191153</v>
+        <v>192047</v>
       </c>
       <c r="AO18" s="13">
-        <v>1133929</v>
+        <v>1134823</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>1.0017483104377403</v>
+        <v>1.0025380979725254</v>
       </c>
       <c r="AQ18" s="7">
         <v>1717059</v>
@@ -3125,14 +3125,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>264945</v>
+        <v>267152</v>
       </c>
       <c r="AT18" s="13">
-        <v>1710743</v>
+        <v>1712950</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.99632161737016611</v>
+        <v>0.99760695468239591</v>
       </c>
       <c r="AV18" s="7">
         <v>1151692</v>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>184537</v>
+        <v>186592</v>
       </c>
       <c r="AY18" s="13">
-        <v>1150054</v>
+        <v>1152109</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.99857774474425454</v>
+        <v>1.0003620759717007</v>
       </c>
       <c r="BA18" s="7">
         <v>1182353</v>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>184223</v>
+        <v>187419</v>
       </c>
       <c r="BD18" s="13">
-        <v>1169806</v>
+        <v>1173002</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.98938810998069104</v>
+        <v>0.99209119442332361</v>
       </c>
       <c r="BF18" s="7">
         <v>1777125</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>344416</v>
+        <v>353848</v>
       </c>
       <c r="BI18" s="6">
-        <v>1741645</v>
+        <v>1751077</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.98003516916367728</v>
+        <v>0.98534261799254419</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3201,14 +3201,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>65971</v>
+        <v>66077</v>
       </c>
       <c r="F19" s="13">
-        <v>299812</v>
+        <v>299918</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.98099921798055745</v>
+        <v>0.98134605505547756</v>
       </c>
       <c r="H19" s="7">
         <v>314567</v>
@@ -3218,14 +3218,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>68506</v>
+        <v>68629</v>
       </c>
       <c r="K19" s="13">
-        <v>306495</v>
+        <v>306618</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.97433932993607086</v>
+        <v>0.97473034361519173</v>
       </c>
       <c r="M19" s="7">
         <v>534704</v>
@@ -3235,14 +3235,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>115109</v>
+        <v>115398</v>
       </c>
       <c r="P19" s="13">
-        <v>526232</v>
+        <v>526521</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.98415571980011374</v>
+        <v>0.98469620575121941</v>
       </c>
       <c r="R19" s="7">
         <v>310887</v>
@@ -3252,14 +3252,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>64502</v>
+        <v>64680</v>
       </c>
       <c r="U19" s="13">
-        <v>305805</v>
+        <v>305983</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.98365322448349402</v>
+        <v>0.98422577978493797</v>
       </c>
       <c r="W19" s="7">
         <v>321022</v>
@@ -3269,14 +3269,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>68307</v>
+        <v>68527</v>
       </c>
       <c r="Z19" s="13">
-        <v>310626</v>
+        <v>310846</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.96761592663431162</v>
+        <v>0.96830123792138856</v>
       </c>
       <c r="AB19" s="7">
         <v>548160</v>
@@ -3286,14 +3286,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>114241</v>
+        <v>114798</v>
       </c>
       <c r="AE19" s="13">
-        <v>536476</v>
+        <v>537033</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.97868505545826034</v>
+        <v>0.9797011821366024</v>
       </c>
       <c r="AG19" s="7">
         <v>315587</v>
@@ -3303,14 +3303,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>67638</v>
+        <v>67972</v>
       </c>
       <c r="AJ19" s="13">
-        <v>309592</v>
+        <v>309926</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.98100365350917496</v>
+        <v>0.98206199875153288</v>
       </c>
       <c r="AL19" s="7">
         <v>327315</v>
@@ -3320,14 +3320,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>62279</v>
+        <v>62762</v>
       </c>
       <c r="AO19" s="13">
-        <v>322347</v>
+        <v>322830</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.98482196049676918</v>
+        <v>0.98629760322624993</v>
       </c>
       <c r="AQ19" s="7">
         <v>564697</v>
@@ -3337,14 +3337,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>107864</v>
+        <v>109180</v>
       </c>
       <c r="AT19" s="13">
-        <v>558907</v>
+        <v>560223</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.9897467137243513</v>
+        <v>0.99207716704710669</v>
       </c>
       <c r="AV19" s="7">
         <v>330794</v>
@@ -3354,14 +3354,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>60398</v>
+        <v>61538</v>
       </c>
       <c r="AY19" s="13">
-        <v>328523</v>
+        <v>329663</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.99313470014571004</v>
+        <v>0.99658095370532718</v>
       </c>
       <c r="BA19" s="7">
         <v>346688</v>
@@ -3371,14 +3371,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>62768</v>
+        <v>64480</v>
       </c>
       <c r="BD19" s="13">
-        <v>337649</v>
+        <v>339361</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.97392756599593866</v>
+        <v>0.97886572364777558</v>
       </c>
       <c r="BF19" s="7">
         <v>595475</v>
@@ -3388,14 +3388,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>138280</v>
+        <v>143924</v>
       </c>
       <c r="BI19" s="6">
-        <v>571907</v>
+        <v>577551</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.96042151223812922</v>
+        <v>0.96989965993534577</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3413,14 +3413,14 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>1765</v>
+        <v>1768</v>
       </c>
       <c r="F20" s="13">
-        <v>6499</v>
+        <v>6502</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.99418693590331952</v>
+        <v>0.99464586201621541</v>
       </c>
       <c r="H20" s="7">
         <v>6601</v>
@@ -3430,14 +3430,14 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="K20" s="13">
-        <v>6525</v>
+        <v>6527</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
-        <v>0.98848659294046359</v>
+        <v>0.9887895773367672</v>
       </c>
       <c r="M20" s="7">
         <v>10050</v>
@@ -3447,14 +3447,14 @@
       </c>
       <c r="O20" s="4">
         <f t="shared" si="4"/>
-        <v>2577</v>
+        <v>2582</v>
       </c>
       <c r="P20" s="13">
-        <v>10020</v>
+        <v>10025</v>
       </c>
       <c r="Q20" s="5">
         <f t="shared" si="5"/>
-        <v>0.9970149253731343</v>
+        <v>0.99751243781094523</v>
       </c>
       <c r="R20" s="7">
         <v>6485</v>
@@ -3464,14 +3464,14 @@
       </c>
       <c r="T20" s="4">
         <f t="shared" si="6"/>
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="U20" s="13">
-        <v>6450</v>
+        <v>6452</v>
       </c>
       <c r="V20" s="5">
         <f t="shared" si="7"/>
-        <v>0.99460292983808785</v>
+        <v>0.99491133384733998</v>
       </c>
       <c r="W20" s="7">
         <v>6573</v>
@@ -3481,14 +3481,14 @@
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="8"/>
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="Z20" s="13">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="9"/>
-        <v>0.98189563365282218</v>
+        <v>0.98219990871748064</v>
       </c>
       <c r="AB20" s="7">
         <v>10123</v>
@@ -3498,14 +3498,14 @@
       </c>
       <c r="AD20" s="4">
         <f t="shared" si="10"/>
-        <v>2640</v>
+        <v>2649</v>
       </c>
       <c r="AE20" s="13">
-        <v>10028</v>
+        <v>10037</v>
       </c>
       <c r="AF20" s="5">
         <f t="shared" si="11"/>
-        <v>0.99061543020843623</v>
+        <v>0.99150449471500546</v>
       </c>
       <c r="AG20" s="7">
         <v>6547</v>
@@ -3515,14 +3515,14 @@
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="12"/>
-        <v>1586</v>
+        <v>1592</v>
       </c>
       <c r="AJ20" s="13">
-        <v>6482</v>
+        <v>6488</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="13"/>
-        <v>0.99007178860546818</v>
+        <v>0.99098823888804033</v>
       </c>
       <c r="AL20" s="7">
         <v>6649</v>
@@ -3532,14 +3532,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1571</v>
+        <v>1577</v>
       </c>
       <c r="AO20" s="13">
-        <v>6560</v>
+        <v>6566</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.98661452850052644</v>
+        <v>0.98751691983756951</v>
       </c>
       <c r="AQ20" s="7">
         <v>10228</v>
@@ -3549,14 +3549,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2430</v>
+        <v>2466</v>
       </c>
       <c r="AT20" s="13">
-        <v>10124</v>
+        <v>10160</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>0.98983183418068044</v>
+        <v>0.99335158388736799</v>
       </c>
       <c r="AV20" s="7">
         <v>6568</v>
@@ -3566,14 +3566,14 @@
       </c>
       <c r="AX20" s="4">
         <f t="shared" si="18"/>
-        <v>1399</v>
+        <v>1422</v>
       </c>
       <c r="AY20" s="13">
-        <v>6483</v>
+        <v>6506</v>
       </c>
       <c r="AZ20" s="5">
         <f t="shared" si="19"/>
-        <v>0.98705846528623631</v>
+        <v>0.99056029232643117</v>
       </c>
       <c r="BA20" s="7">
         <v>6793</v>
@@ -3583,14 +3583,14 @@
       </c>
       <c r="BC20" s="4">
         <f t="shared" si="20"/>
-        <v>1405</v>
+        <v>1441</v>
       </c>
       <c r="BD20" s="13">
-        <v>6529</v>
+        <v>6565</v>
       </c>
       <c r="BE20" s="5">
         <f t="shared" si="21"/>
-        <v>0.96113646400706609</v>
+        <v>0.96643603709701165</v>
       </c>
       <c r="BF20" s="7">
         <v>10395</v>
@@ -3600,14 +3600,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>2536</v>
+        <v>2643</v>
       </c>
       <c r="BI20" s="6">
-        <v>10034</v>
+        <v>10141</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>0.96527176527176528</v>
+        <v>0.97556517556517552</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3625,14 +3625,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>4194</v>
+        <v>4207</v>
       </c>
       <c r="F21" s="13">
-        <v>12072</v>
+        <v>12085</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>1.0051623646960866</v>
+        <v>1.0062447960033305</v>
       </c>
       <c r="H21" s="7">
         <v>12254</v>
@@ -3642,14 +3642,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3828</v>
+        <v>3845</v>
       </c>
       <c r="K21" s="13">
-        <v>12282</v>
+        <v>12299</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>1.0022849681736576</v>
+        <v>1.0036722702790926</v>
       </c>
       <c r="M21" s="7">
         <v>16207</v>
@@ -3659,14 +3659,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>5127</v>
+        <v>5153</v>
       </c>
       <c r="P21" s="13">
-        <v>16383</v>
+        <v>16409</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>1.0108595051520948</v>
+        <v>1.0124637502313816</v>
       </c>
       <c r="R21" s="7">
         <v>12383</v>
@@ -3676,14 +3676,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3937</v>
+        <v>3959</v>
       </c>
       <c r="U21" s="13">
-        <v>12582</v>
+        <v>12604</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>1.0160704191229912</v>
+        <v>1.0178470483727691</v>
       </c>
       <c r="W21" s="7">
         <v>12782</v>
@@ -3693,14 +3693,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>4005</v>
+        <v>4029</v>
       </c>
       <c r="Z21" s="13">
-        <v>12796</v>
+        <v>12820</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>1.0010952902519168</v>
+        <v>1.002972930683774</v>
       </c>
       <c r="AB21" s="7">
         <v>16816</v>
@@ -3710,14 +3710,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4714</v>
+        <v>4755</v>
       </c>
       <c r="AE21" s="13">
-        <v>16867</v>
+        <v>16908</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>1.0030328258801142</v>
+        <v>1.0054709800190296</v>
       </c>
       <c r="AG21" s="7">
         <v>12696</v>
@@ -3727,14 +3727,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3933</v>
+        <v>3966</v>
       </c>
       <c r="AJ21" s="13">
-        <v>12768</v>
+        <v>12801</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>1.005671077504726</v>
+        <v>1.0082703213610587</v>
       </c>
       <c r="AL21" s="7">
         <v>13072</v>
@@ -3744,14 +3744,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3889</v>
+        <v>3938</v>
       </c>
       <c r="AO21" s="13">
-        <v>13018</v>
+        <v>13067</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>0.99586903304773566</v>
+        <v>0.99961750305997554</v>
       </c>
       <c r="AQ21" s="7">
         <v>17310</v>
@@ -3761,14 +3761,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4616</v>
+        <v>4709</v>
       </c>
       <c r="AT21" s="13">
-        <v>17242</v>
+        <v>17335</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>0.99607163489312533</v>
+        <v>1.0014442518775275</v>
       </c>
       <c r="AV21" s="7">
         <v>13094</v>
@@ -3778,14 +3778,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3490</v>
+        <v>3582</v>
       </c>
       <c r="AY21" s="13">
-        <v>12979</v>
+        <v>13071</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>0.99121735145868339</v>
+        <v>0.99824347029173666</v>
       </c>
       <c r="BA21" s="7">
         <v>13518</v>
@@ -3795,14 +3795,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3322</v>
+        <v>3455</v>
       </c>
       <c r="BD21" s="13">
-        <v>13103</v>
+        <v>13236</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>0.9693001923361444</v>
+        <v>0.979138925876609</v>
       </c>
       <c r="BF21" s="7">
         <v>17905</v>
@@ -3812,14 +3812,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>5802</v>
+        <v>6160</v>
       </c>
       <c r="BI21" s="6">
-        <v>16746</v>
+        <v>17104</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>0.93526947779949732</v>
+        <v>0.95526389276738344</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3837,14 +3837,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1898</v>
+        <v>1906</v>
       </c>
       <c r="F22" s="13">
-        <v>6992</v>
+        <v>7000</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.99942824471126357</v>
+        <v>1.0005717552887363</v>
       </c>
       <c r="H22" s="7">
         <v>7077</v>
@@ -3854,14 +3854,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1957</v>
+        <v>1964</v>
       </c>
       <c r="K22" s="13">
-        <v>7049</v>
+        <v>7056</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>0.99604352126607321</v>
+        <v>0.9970326409495549</v>
       </c>
       <c r="M22" s="7">
         <v>8504</v>
@@ -3871,14 +3871,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>2417</v>
+        <v>2427</v>
       </c>
       <c r="P22" s="13">
-        <v>8535</v>
+        <v>8545</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>1.003645343367827</v>
+        <v>1.0048212605832549</v>
       </c>
       <c r="R22" s="7">
         <v>7111</v>
@@ -3888,14 +3888,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1855</v>
+        <v>1863</v>
       </c>
       <c r="U22" s="13">
-        <v>7096</v>
+        <v>7104</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>0.99789059204050068</v>
+        <v>0.99901560961890035</v>
       </c>
       <c r="W22" s="7">
         <v>7191</v>
@@ -3905,14 +3905,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="Z22" s="13">
-        <v>7155</v>
+        <v>7163</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>0.99499374217772218</v>
+        <v>0.99610624391600611</v>
       </c>
       <c r="AB22" s="7">
         <v>8707</v>
@@ -3922,14 +3922,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2055</v>
+        <v>2066</v>
       </c>
       <c r="AE22" s="13">
-        <v>8684</v>
+        <v>8695</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>0.99735844722636957</v>
+        <v>0.99862179855288846</v>
       </c>
       <c r="AG22" s="7">
         <v>7162</v>
@@ -3939,14 +3939,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1863</v>
+        <v>1874</v>
       </c>
       <c r="AJ22" s="13">
-        <v>7160</v>
+        <v>7171</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>0.99972074839430325</v>
+        <v>1.0012566322256353</v>
       </c>
       <c r="AL22" s="7">
         <v>7226</v>
@@ -3956,14 +3956,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1688</v>
+        <v>1704</v>
       </c>
       <c r="AO22" s="13">
-        <v>7200</v>
+        <v>7216</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.99640188209244396</v>
+        <v>0.99861610849709381</v>
       </c>
       <c r="AQ22" s="7">
         <v>8754</v>
@@ -3973,14 +3973,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2395</v>
+        <v>2423</v>
       </c>
       <c r="AT22" s="13">
-        <v>8741</v>
+        <v>8769</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>0.99851496458761713</v>
+        <v>1.0017135023989034</v>
       </c>
       <c r="AV22" s="7">
         <v>7182</v>
@@ -3990,14 +3990,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1767</v>
+        <v>1795</v>
       </c>
       <c r="AY22" s="13">
-        <v>7153</v>
+        <v>7181</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.99596212754107494</v>
+        <v>0.99986076301865778</v>
       </c>
       <c r="BA22" s="7">
         <v>7296</v>
@@ -4007,14 +4007,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1683</v>
+        <v>1729</v>
       </c>
       <c r="BD22" s="13">
-        <v>7180</v>
+        <v>7226</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>0.98410087719298245</v>
+        <v>0.99040570175438591</v>
       </c>
       <c r="BF22" s="7">
         <v>8939</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2452</v>
+        <v>2566</v>
       </c>
       <c r="BI22" s="6">
-        <v>8558</v>
+        <v>8672</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>0.95737778274974827</v>
+        <v>0.97013088712383932</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4049,14 +4049,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>2960</v>
+        <v>2972</v>
       </c>
       <c r="F23" s="13">
-        <v>9193</v>
+        <v>9205</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.9772509833103008</v>
+        <v>0.97852662910598487</v>
       </c>
       <c r="H23" s="7">
         <v>9786</v>
@@ -4066,14 +4066,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>3247</v>
+        <v>3258</v>
       </c>
       <c r="K23" s="13">
-        <v>9321</v>
+        <v>9332</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.9524831391784182</v>
+        <v>0.95360719395054161</v>
       </c>
       <c r="M23" s="7">
         <v>12056</v>
@@ -4083,14 +4083,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>4021</v>
+        <v>4036</v>
       </c>
       <c r="P23" s="13">
-        <v>11874</v>
+        <v>11889</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.98490378234903786</v>
+        <v>0.98614797611147975</v>
       </c>
       <c r="R23" s="7">
         <v>9480</v>
@@ -4100,14 +4100,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>2972</v>
+        <v>2987</v>
       </c>
       <c r="U23" s="13">
-        <v>9399</v>
+        <v>9414</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.9914556962025316</v>
+        <v>0.99303797468354427</v>
       </c>
       <c r="W23" s="7">
         <v>9764</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>3056</v>
+        <v>3071</v>
       </c>
       <c r="Z23" s="13">
-        <v>9475</v>
+        <v>9490</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.97040147480540762</v>
+        <v>0.97193773043834497</v>
       </c>
       <c r="AB23" s="7">
         <v>12327</v>
@@ -4134,14 +4134,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3551</v>
+        <v>3573</v>
       </c>
       <c r="AE23" s="13">
-        <v>12092</v>
+        <v>12114</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.98093615640464027</v>
+        <v>0.98272085665612074</v>
       </c>
       <c r="AG23" s="7">
         <v>9618</v>
@@ -4151,14 +4151,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>3054</v>
+        <v>3078</v>
       </c>
       <c r="AJ23" s="13">
-        <v>9390</v>
+        <v>9414</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.97629444791016839</v>
+        <v>0.97878976918278227</v>
       </c>
       <c r="AL23" s="7">
         <v>9741</v>
@@ -4168,14 +4168,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2903</v>
+        <v>2941</v>
       </c>
       <c r="AO23" s="13">
-        <v>9539</v>
+        <v>9577</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.9792629093522226</v>
+        <v>0.98316394620675496</v>
       </c>
       <c r="AQ23" s="7">
         <v>12556</v>
@@ -4185,14 +4185,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3645</v>
+        <v>3705</v>
       </c>
       <c r="AT23" s="13">
-        <v>12271</v>
+        <v>12331</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>0.97730168843580756</v>
+        <v>0.98208028034405859</v>
       </c>
       <c r="AV23" s="7">
         <v>9718</v>
@@ -4202,14 +4202,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2668</v>
+        <v>2756</v>
       </c>
       <c r="AY23" s="13">
-        <v>9532</v>
+        <v>9620</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>0.98086025931261578</v>
+        <v>0.98991562049804482</v>
       </c>
       <c r="BA23" s="7">
         <v>10107</v>
@@ -4219,14 +4219,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2844</v>
+        <v>2955</v>
       </c>
       <c r="BD23" s="13">
-        <v>9679</v>
+        <v>9790</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.95765311170475909</v>
+        <v>0.96863559908973973</v>
       </c>
       <c r="BF23" s="7">
         <v>13018</v>
@@ -4236,14 +4236,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4179</v>
+        <v>4398</v>
       </c>
       <c r="BI23" s="6">
-        <v>12186</v>
+        <v>12405</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.93608849285604545</v>
+        <v>0.95291135351052392</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4261,14 +4261,14 @@
       </c>
       <c r="E24" s="4">
         <f t="shared" si="0"/>
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="F24" s="13">
-        <v>6894</v>
+        <v>6897</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.99308556611927401</v>
+        <v>0.99351771823681934</v>
       </c>
       <c r="H24" s="7">
         <v>7059</v>
@@ -4278,14 +4278,14 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" si="2"/>
-        <v>1594</v>
+        <v>1600</v>
       </c>
       <c r="K24" s="13">
-        <v>6949</v>
+        <v>6955</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="3"/>
-        <v>0.98441705624026066</v>
+        <v>0.98526703499079193</v>
       </c>
       <c r="M24" s="7">
         <v>8056</v>
@@ -4295,14 +4295,14 @@
       </c>
       <c r="O24" s="4">
         <f t="shared" si="4"/>
-        <v>1774</v>
+        <v>1784</v>
       </c>
       <c r="P24" s="13">
-        <v>7937</v>
+        <v>7947</v>
       </c>
       <c r="Q24" s="5">
         <f t="shared" si="5"/>
-        <v>0.98522840119165844</v>
+        <v>0.98646971201588873</v>
       </c>
       <c r="R24" s="7">
         <v>7134</v>
@@ -4312,14 +4312,14 @@
       </c>
       <c r="T24" s="4">
         <f t="shared" si="6"/>
-        <v>1395</v>
+        <v>1402</v>
       </c>
       <c r="U24" s="13">
-        <v>7017</v>
+        <v>7024</v>
       </c>
       <c r="V24" s="5">
         <f t="shared" si="7"/>
-        <v>0.98359966358284268</v>
+        <v>0.98458088029156154</v>
       </c>
       <c r="W24" s="7">
         <v>7208</v>
@@ -4329,14 +4329,14 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="8"/>
-        <v>1449</v>
+        <v>1459</v>
       </c>
       <c r="Z24" s="13">
-        <v>7068</v>
+        <v>7078</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="9"/>
-        <v>0.98057713651498335</v>
+        <v>0.98196448390677027</v>
       </c>
       <c r="AB24" s="7">
         <v>8228</v>
@@ -4346,14 +4346,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1266</v>
+        <v>1282</v>
       </c>
       <c r="AE24" s="13">
-        <v>8080</v>
+        <v>8096</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.98201263976665043</v>
+        <v>0.98395721925133695</v>
       </c>
       <c r="AG24" s="7">
         <v>7344</v>
@@ -4363,14 +4363,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1432</v>
+        <v>1451</v>
       </c>
       <c r="AJ24" s="13">
-        <v>7177</v>
+        <v>7196</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.977260348583878</v>
+        <v>0.97984749455337694</v>
       </c>
       <c r="AL24" s="7">
         <v>7506</v>
@@ -4380,14 +4380,14 @@
       </c>
       <c r="AN24" s="4">
         <f t="shared" si="14"/>
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="AO24" s="13">
-        <v>7284</v>
+        <v>7303</v>
       </c>
       <c r="AP24" s="5">
         <f t="shared" si="15"/>
-        <v>0.97042366107114308</v>
+        <v>0.97295496935784709</v>
       </c>
       <c r="AQ24" s="7">
         <v>8509</v>
@@ -4397,14 +4397,14 @@
       </c>
       <c r="AS24" s="4">
         <f t="shared" si="16"/>
-        <v>1583</v>
+        <v>1613</v>
       </c>
       <c r="AT24" s="13">
-        <v>8277</v>
+        <v>8307</v>
       </c>
       <c r="AU24" s="5">
         <f t="shared" si="17"/>
-        <v>0.97273475143965216</v>
+        <v>0.97626043013280062</v>
       </c>
       <c r="AV24" s="7">
         <v>7570</v>
@@ -4414,14 +4414,14 @@
       </c>
       <c r="AX24" s="4">
         <f t="shared" si="18"/>
-        <v>1279</v>
+        <v>1310</v>
       </c>
       <c r="AY24" s="13">
-        <v>7322</v>
+        <v>7353</v>
       </c>
       <c r="AZ24" s="5">
         <f t="shared" si="19"/>
-        <v>0.96723910171730521</v>
+        <v>0.97133421400264197</v>
       </c>
       <c r="BA24" s="7">
         <v>7648</v>
@@ -4431,14 +4431,14 @@
       </c>
       <c r="BC24" s="4">
         <f t="shared" si="20"/>
-        <v>1449</v>
+        <v>1490</v>
       </c>
       <c r="BD24" s="13">
-        <v>7443</v>
+        <v>7484</v>
       </c>
       <c r="BE24" s="5">
         <f t="shared" si="21"/>
-        <v>0.97319560669456062</v>
+        <v>0.97855648535564854</v>
       </c>
       <c r="BF24" s="7">
         <v>8767</v>
@@ -4448,14 +4448,14 @@
       </c>
       <c r="BH24" s="4">
         <f t="shared" si="22"/>
-        <v>1692</v>
+        <v>1770</v>
       </c>
       <c r="BI24" s="6">
-        <v>8459</v>
+        <v>8537</v>
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="23"/>
-        <v>0.96486825595984949</v>
+        <v>0.97376525607391351</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4473,14 +4473,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>4692</v>
+        <v>4701</v>
       </c>
       <c r="F25" s="13">
-        <v>21352</v>
+        <v>21361</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.99436501653238951</v>
+        <v>0.99478414753411259</v>
       </c>
       <c r="H25" s="7">
         <v>21813</v>
@@ -4490,14 +4490,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>4522</v>
+        <v>4535</v>
       </c>
       <c r="K25" s="13">
-        <v>21544</v>
+        <v>21557</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>0.98766790446064279</v>
+        <v>0.98826387933800941</v>
       </c>
       <c r="M25" s="7">
         <v>29215</v>
@@ -4507,14 +4507,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>6228</v>
+        <v>6249</v>
       </c>
       <c r="P25" s="13">
-        <v>29019</v>
+        <v>29040</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>0.99329111757658739</v>
+        <v>0.99400992640766728</v>
       </c>
       <c r="R25" s="7">
         <v>21767</v>
@@ -4524,14 +4524,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>4548</v>
+        <v>4562</v>
       </c>
       <c r="U25" s="13">
-        <v>21639</v>
+        <v>21653</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>0.99411953875132075</v>
+        <v>0.99476271420039508</v>
       </c>
       <c r="W25" s="7">
         <v>22114</v>
@@ -4541,14 +4541,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>4246</v>
+        <v>4262</v>
       </c>
       <c r="Z25" s="13">
-        <v>21772</v>
+        <v>21788</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.9845346839106448</v>
+        <v>0.98525820747038073</v>
       </c>
       <c r="AB25" s="7">
         <v>29630</v>
@@ -4558,14 +4558,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>5493</v>
+        <v>5523</v>
       </c>
       <c r="AE25" s="13">
-        <v>29379</v>
+        <v>29409</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>0.9915288558893014</v>
+        <v>0.99254134323320964</v>
       </c>
       <c r="AG25" s="7">
         <v>22174</v>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>4385</v>
+        <v>4410</v>
       </c>
       <c r="AJ25" s="13">
-        <v>21900</v>
+        <v>21925</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>0.98764318571299725</v>
+        <v>0.98877063227203033</v>
       </c>
       <c r="AL25" s="7">
         <v>22503</v>
@@ -4592,14 +4592,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>4316</v>
+        <v>4346</v>
       </c>
       <c r="AO25" s="13">
-        <v>22278</v>
+        <v>22308</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.99000133315557926</v>
+        <v>0.99133448873483532</v>
       </c>
       <c r="AQ25" s="7">
         <v>30294</v>
@@ -4609,14 +4609,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>5681</v>
+        <v>5746</v>
       </c>
       <c r="AT25" s="13">
-        <v>30013</v>
+        <v>30078</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>0.99072423582227509</v>
+        <v>0.99286987522281644</v>
       </c>
       <c r="AV25" s="7">
         <v>22740</v>
@@ -4626,14 +4626,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>4325</v>
+        <v>4386</v>
       </c>
       <c r="AY25" s="13">
-        <v>22588</v>
+        <v>22649</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>0.9933157431838171</v>
+        <v>0.99599824098504841</v>
       </c>
       <c r="BA25" s="7">
         <v>23197</v>
@@ -4643,14 +4643,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>4162</v>
+        <v>4250</v>
       </c>
       <c r="BD25" s="13">
-        <v>22817</v>
+        <v>22905</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>0.98361857136698716</v>
+        <v>0.98741216536621113</v>
       </c>
       <c r="BF25" s="7">
         <v>31043</v>
@@ -4660,14 +4660,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>7126</v>
+        <v>7353</v>
       </c>
       <c r="BI25" s="6">
-        <v>30194</v>
+        <v>30421</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>0.97265083915858652</v>
+        <v>0.97996327674515993</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4685,14 +4685,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3326</v>
+        <v>3342</v>
       </c>
       <c r="F26" s="13">
-        <v>14472</v>
+        <v>14488</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.99450247388675095</v>
+        <v>0.99560197910940074</v>
       </c>
       <c r="H26" s="7">
         <v>14990</v>
@@ -4702,14 +4702,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3306</v>
+        <v>3327</v>
       </c>
       <c r="K26" s="13">
-        <v>14785</v>
+        <v>14806</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>0.98632421614409604</v>
+        <v>0.98772515010006667</v>
       </c>
       <c r="M26" s="7">
         <v>28508</v>
@@ -4719,14 +4719,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5965</v>
+        <v>5998</v>
       </c>
       <c r="P26" s="13">
-        <v>28404</v>
+        <v>28437</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>0.99635190122070993</v>
+        <v>0.997509471025677</v>
       </c>
       <c r="R26" s="7">
         <v>14719</v>
@@ -4736,14 +4736,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3412</v>
+        <v>3435</v>
       </c>
       <c r="U26" s="13">
-        <v>14659</v>
+        <v>14682</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>0.99592363611658397</v>
+        <v>0.99748624227189342</v>
       </c>
       <c r="W26" s="7">
         <v>15123</v>
@@ -4753,14 +4753,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3457</v>
+        <v>3483</v>
       </c>
       <c r="Z26" s="13">
-        <v>14828</v>
+        <v>14854</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.98049328836870986</v>
+        <v>0.98221252397011172</v>
       </c>
       <c r="AB26" s="7">
         <v>29054</v>
@@ -4770,14 +4770,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5160</v>
+        <v>5208</v>
       </c>
       <c r="AE26" s="13">
-        <v>28738</v>
+        <v>28786</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.98912370069525712</v>
+        <v>0.99077579679218009</v>
       </c>
       <c r="AG26" s="7">
         <v>14835</v>
@@ -4787,14 +4787,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3308</v>
+        <v>3343</v>
       </c>
       <c r="AJ26" s="13">
-        <v>14669</v>
+        <v>14704</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>0.98881024603977086</v>
+        <v>0.99116953151331311</v>
       </c>
       <c r="AL26" s="7">
         <v>15316</v>
@@ -4804,14 +4804,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>3247</v>
+        <v>3292</v>
       </c>
       <c r="AO26" s="13">
-        <v>14933</v>
+        <v>14978</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.97499347088012533</v>
+        <v>0.97793157482371373</v>
       </c>
       <c r="AQ26" s="7">
         <v>29312</v>
@@ -4821,14 +4821,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5485</v>
+        <v>5588</v>
       </c>
       <c r="AT26" s="13">
-        <v>29013</v>
+        <v>29116</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.98979939956331875</v>
+        <v>0.99331331877729256</v>
       </c>
       <c r="AV26" s="7">
         <v>15164</v>
@@ -4838,14 +4838,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>2978</v>
+        <v>3079</v>
       </c>
       <c r="AY26" s="13">
-        <v>14974</v>
+        <v>15075</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.98747032445265104</v>
+        <v>0.99413083619097864</v>
       </c>
       <c r="BA26" s="7">
         <v>15499</v>
@@ -4855,14 +4855,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3067</v>
+        <v>3213</v>
       </c>
       <c r="BD26" s="13">
-        <v>14978</v>
+        <v>15124</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.96638492805987486</v>
+        <v>0.97580489063810572</v>
       </c>
       <c r="BF26" s="7">
         <v>29635</v>
@@ -4872,14 +4872,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>5832</v>
+        <v>6155</v>
       </c>
       <c r="BI26" s="6">
-        <v>28696</v>
+        <v>29019</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.96831449299814409</v>
+        <v>0.97921376750463973</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4897,14 +4897,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>34762</v>
+        <v>34828</v>
       </c>
       <c r="F27" s="13">
-        <v>129757</v>
+        <v>129823</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>0.98954456714050398</v>
+        <v>0.99004789213592825</v>
       </c>
       <c r="H27" s="7">
         <v>134384</v>
@@ -4914,14 +4914,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>33918</v>
+        <v>33999</v>
       </c>
       <c r="K27" s="13">
-        <v>130722</v>
+        <v>130803</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.9727497321109656</v>
+        <v>0.97335248243838557</v>
       </c>
       <c r="M27" s="7">
         <v>190911</v>
@@ -4931,14 +4931,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>51071</v>
+        <v>51254</v>
       </c>
       <c r="P27" s="13">
-        <v>190860</v>
+        <v>191043</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.99973285981425897</v>
+        <v>1.000691421657212</v>
       </c>
       <c r="R27" s="7">
         <v>131264</v>
@@ -4948,14 +4948,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>32999</v>
+        <v>33124</v>
       </c>
       <c r="U27" s="13">
-        <v>130557</v>
+        <v>130682</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.99461390784982939</v>
+        <v>0.99556618722574353</v>
       </c>
       <c r="W27" s="7">
         <v>134144</v>
@@ -4965,14 +4965,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>37529</v>
+        <v>37665</v>
       </c>
       <c r="Z27" s="13">
-        <v>131800</v>
+        <v>131936</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.98252624045801529</v>
+        <v>0.98354007633587781</v>
       </c>
       <c r="AB27" s="7">
         <v>194609</v>
@@ -4982,14 +4982,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>48493</v>
+        <v>48792</v>
       </c>
       <c r="AE27" s="13">
-        <v>193077</v>
+        <v>193376</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.99212780498332553</v>
+        <v>0.99366421902378621</v>
       </c>
       <c r="AG27" s="7">
         <v>134089</v>
@@ -4999,14 +4999,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>33887</v>
+        <v>34093</v>
       </c>
       <c r="AJ27" s="13">
-        <v>132236</v>
+        <v>132442</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.98618082020150799</v>
+        <v>0.98771711326059553</v>
       </c>
       <c r="AL27" s="7">
         <v>137688</v>
@@ -5016,14 +5016,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>32314</v>
+        <v>32596</v>
       </c>
       <c r="AO27" s="13">
-        <v>136436</v>
+        <v>136718</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.99090697809540407</v>
+        <v>0.99295508686305267</v>
       </c>
       <c r="AQ27" s="7">
         <v>200322</v>
@@ -5033,14 +5033,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>48910</v>
+        <v>49593</v>
       </c>
       <c r="AT27" s="13">
-        <v>199199</v>
+        <v>199882</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.99439402561875379</v>
+        <v>0.9978035363065465</v>
       </c>
       <c r="AV27" s="7">
         <v>139481</v>
@@ -5050,14 +5050,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>30447</v>
+        <v>31071</v>
       </c>
       <c r="AY27" s="13">
-        <v>137689</v>
+        <v>138313</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.98715237200765693</v>
+        <v>0.99162609961213355</v>
       </c>
       <c r="BA27" s="7">
         <v>143305</v>
@@ -5067,14 +5067,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>30972</v>
+        <v>31964</v>
       </c>
       <c r="BD27" s="13">
-        <v>139389</v>
+        <v>140381</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.97267366805066113</v>
+        <v>0.97959596664456927</v>
       </c>
       <c r="BF27" s="7">
         <v>208143</v>
@@ -5084,14 +5084,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>59056</v>
+        <v>61673</v>
       </c>
       <c r="BI27" s="6">
-        <v>199183</v>
+        <v>201800</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.95695267196110367</v>
+        <v>0.96952575873317859</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5109,14 +5109,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>70261</v>
+        <v>70341</v>
       </c>
       <c r="F28" s="13">
-        <v>435116</v>
+        <v>435196</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.99452130565263208</v>
+        <v>0.99470415736218121</v>
       </c>
       <c r="H28" s="7">
         <v>447363</v>
@@ -5126,14 +5126,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>70439</v>
+        <v>70539</v>
       </c>
       <c r="K28" s="13">
-        <v>442536</v>
+        <v>442636</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.98921010454597269</v>
+        <v>0.98943363666642081</v>
       </c>
       <c r="M28" s="7">
         <v>722935</v>
@@ -5143,14 +5143,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>118143</v>
+        <v>118374</v>
       </c>
       <c r="P28" s="13">
-        <v>717582</v>
+        <v>717813</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.99259546155601819</v>
+        <v>0.99291499235754255</v>
       </c>
       <c r="R28" s="7">
         <v>448339</v>
@@ -5160,14 +5160,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>69829</v>
+        <v>69984</v>
       </c>
       <c r="U28" s="13">
-        <v>445729</v>
+        <v>445884</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.99417851224185272</v>
+        <v>0.99452423277921398</v>
       </c>
       <c r="W28" s="7">
         <v>458076</v>
@@ -5177,14 +5177,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>73771</v>
+        <v>73964</v>
       </c>
       <c r="Z28" s="13">
-        <v>450712</v>
+        <v>450905</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.983924065002314</v>
+        <v>0.98434539246762542</v>
       </c>
       <c r="AB28" s="7">
         <v>737235</v>
@@ -5194,14 +5194,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>114172</v>
+        <v>114621</v>
       </c>
       <c r="AE28" s="13">
-        <v>729694</v>
+        <v>730143</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.98977123983533066</v>
+        <v>0.99038027223341263</v>
       </c>
       <c r="AG28" s="7">
         <v>456666</v>
@@ -5211,14 +5211,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>71399</v>
+        <v>71710</v>
       </c>
       <c r="AJ28" s="13">
-        <v>451603</v>
+        <v>451914</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.98891312250090879</v>
+        <v>0.98959414539291302</v>
       </c>
       <c r="AL28" s="7">
         <v>468801</v>
@@ -5228,14 +5228,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>69537</v>
+        <v>70015</v>
       </c>
       <c r="AO28" s="13">
-        <v>464774</v>
+        <v>465252</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.99141000125852974</v>
+        <v>0.99242962365694609</v>
       </c>
       <c r="AQ28" s="7">
         <v>756132</v>
@@ -5245,14 +5245,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>107708</v>
+        <v>108942</v>
       </c>
       <c r="AT28" s="13">
-        <v>751282</v>
+        <v>752516</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.99358577602852416</v>
+        <v>0.99521776621013258</v>
       </c>
       <c r="AV28" s="7">
         <v>474991</v>
@@ -5262,14 +5262,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>65683</v>
+        <v>66876</v>
       </c>
       <c r="AY28" s="13">
-        <v>470718</v>
+        <v>471911</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.99100404007654885</v>
+        <v>0.99351566661263058</v>
       </c>
       <c r="BA28" s="7">
         <v>487540</v>
@@ -5279,14 +5279,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>67125</v>
+        <v>69033</v>
       </c>
       <c r="BD28" s="13">
-        <v>477889</v>
+        <v>479797</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.98020470115272595</v>
+        <v>0.98411822619682487</v>
       </c>
       <c r="BF28" s="7">
         <v>779284</v>
@@ -5296,14 +5296,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>134020</v>
+        <v>139594</v>
       </c>
       <c r="BI28" s="6">
-        <v>758218</v>
+        <v>763792</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.97296749323738196</v>
+        <v>0.98012021291339224</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>28190</v>
+        <v>28227</v>
       </c>
       <c r="F29" s="13">
-        <v>142697</v>
+        <v>142734</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.99266097167343759</v>
+        <v>0.99291835939673878</v>
       </c>
       <c r="H29" s="7">
         <v>146310</v>
@@ -5338,14 +5338,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>27552</v>
+        <v>27593</v>
       </c>
       <c r="K29" s="13">
-        <v>144147</v>
+        <v>144188</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.98521632150912442</v>
+        <v>0.9854965484245779</v>
       </c>
       <c r="M29" s="7">
         <v>194093</v>
@@ -5355,14 +5355,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>37738</v>
+        <v>37810</v>
       </c>
       <c r="P29" s="13">
-        <v>191590</v>
+        <v>191662</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.98710412018980587</v>
+        <v>0.98747507638091014</v>
       </c>
       <c r="R29" s="7">
         <v>146918</v>
@@ -5372,14 +5372,14 @@
       </c>
       <c r="T29" s="4">
         <f t="shared" si="6"/>
-        <v>26637</v>
+        <v>26692</v>
       </c>
       <c r="U29" s="13">
-        <v>145186</v>
+        <v>145241</v>
       </c>
       <c r="V29" s="5">
         <f t="shared" si="7"/>
-        <v>0.98821111095985514</v>
+        <v>0.98858546944554104</v>
       </c>
       <c r="W29" s="7">
         <v>149105</v>
@@ -5389,14 +5389,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>27052</v>
+        <v>27120</v>
       </c>
       <c r="Z29" s="13">
-        <v>146470</v>
+        <v>146538</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.98232788974212804</v>
+        <v>0.98278394420039572</v>
       </c>
       <c r="AB29" s="7">
         <v>197403</v>
@@ -5406,14 +5406,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>33007</v>
+        <v>33134</v>
       </c>
       <c r="AE29" s="13">
-        <v>194541</v>
+        <v>194668</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.98550174009513536</v>
+        <v>0.98614509404618977</v>
       </c>
       <c r="AG29" s="7">
         <v>149309</v>
@@ -5423,14 +5423,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>27660</v>
+        <v>27763</v>
       </c>
       <c r="AJ29" s="13">
-        <v>147331</v>
+        <v>147434</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.98675230562122851</v>
+        <v>0.98744215017179138</v>
       </c>
       <c r="AL29" s="7">
         <v>152026</v>
@@ -5440,14 +5440,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>25990</v>
+        <v>26139</v>
       </c>
       <c r="AO29" s="13">
-        <v>152003</v>
+        <v>152152</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.99984871008906373</v>
+        <v>1.0008288055990422</v>
       </c>
       <c r="AQ29" s="7">
         <v>203571</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>34406</v>
+        <v>34775</v>
       </c>
       <c r="AT29" s="13">
-        <v>202620</v>
+        <v>202989</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.99532841121770788</v>
+        <v>0.99714104661272973</v>
       </c>
       <c r="AV29" s="7">
         <v>155780</v>
@@ -5474,14 +5474,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>25710</v>
+        <v>26143</v>
       </c>
       <c r="AY29" s="13">
-        <v>155059</v>
+        <v>155492</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.99537167800744641</v>
+        <v>0.99815123892669144</v>
       </c>
       <c r="BA29" s="7">
         <v>159604</v>
@@ -5491,14 +5491,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>26300</v>
+        <v>26984</v>
       </c>
       <c r="BD29" s="13">
-        <v>157366</v>
+        <v>158050</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.98597779504273075</v>
+        <v>0.99026340191975137</v>
       </c>
       <c r="BF29" s="7">
         <v>211893</v>
@@ -5508,14 +5508,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>41987</v>
+        <v>43558</v>
       </c>
       <c r="BI29" s="6">
-        <v>206357</v>
+        <v>207928</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.97387360601813178</v>
+        <v>0.98128772540857889</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5533,14 +5533,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>41218</v>
+        <v>41253</v>
       </c>
       <c r="F30" s="13">
-        <v>185582</v>
+        <v>185617</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.99629573956364881</v>
+        <v>0.99648363683215946</v>
       </c>
       <c r="H30" s="7">
         <v>190966</v>
@@ -5550,14 +5550,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>41630</v>
+        <v>41678</v>
       </c>
       <c r="K30" s="13">
-        <v>188442</v>
+        <v>188490</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.98678298754752158</v>
+        <v>0.9870343411916257</v>
       </c>
       <c r="M30" s="7">
         <v>320227</v>
@@ -5567,14 +5567,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>67780</v>
+        <v>67874</v>
       </c>
       <c r="P30" s="13">
-        <v>317782</v>
+        <v>317876</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.9923647912262239</v>
+        <v>0.9926583329950317</v>
       </c>
       <c r="R30" s="7">
         <v>189502</v>
@@ -5584,14 +5584,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>37962</v>
+        <v>38019</v>
       </c>
       <c r="U30" s="13">
-        <v>188477</v>
+        <v>188534</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.99459108610990909</v>
+        <v>0.99489187449208982</v>
       </c>
       <c r="W30" s="7">
         <v>194334</v>
@@ -5601,14 +5601,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>37855</v>
+        <v>37921</v>
       </c>
       <c r="Z30" s="13">
-        <v>190733</v>
+        <v>190799</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.98147004641493507</v>
+        <v>0.98180966789136226</v>
       </c>
       <c r="AB30" s="7">
         <v>325942</v>
@@ -5618,14 +5618,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>60673</v>
+        <v>60845</v>
       </c>
       <c r="AE30" s="13">
-        <v>322615</v>
+        <v>322787</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.98979266249823583</v>
+        <v>0.9903203637456971</v>
       </c>
       <c r="AG30" s="7">
         <v>192789</v>
@@ -5635,14 +5635,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>39891</v>
+        <v>40019</v>
       </c>
       <c r="AJ30" s="13">
-        <v>191370</v>
+        <v>191498</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.99263962155517171</v>
+        <v>0.99330355985040641</v>
       </c>
       <c r="AL30" s="7">
         <v>197994</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>37399</v>
+        <v>37609</v>
       </c>
       <c r="AO30" s="13">
-        <v>196173</v>
+        <v>196383</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.99080275159853326</v>
+        <v>0.99186338979969091</v>
       </c>
       <c r="AQ30" s="7">
         <v>333633</v>
@@ -5669,14 +5669,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>61047</v>
+        <v>61590</v>
       </c>
       <c r="AT30" s="13">
-        <v>331190</v>
+        <v>331733</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.99267758285301511</v>
+        <v>0.99430511969739199</v>
       </c>
       <c r="AV30" s="7">
         <v>198460</v>
@@ -5686,14 +5686,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>36859</v>
+        <v>37380</v>
       </c>
       <c r="AY30" s="13">
-        <v>197154</v>
+        <v>197675</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.99341932883200645</v>
+        <v>0.99604454298095335</v>
       </c>
       <c r="BA30" s="7">
         <v>203942</v>
@@ -5703,14 +5703,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>37718</v>
+        <v>38575</v>
       </c>
       <c r="BD30" s="13">
-        <v>199990</v>
+        <v>200847</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.98062194153239646</v>
+        <v>0.9848241166606192</v>
       </c>
       <c r="BF30" s="7">
         <v>342999</v>
@@ -5720,14 +5720,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>76346</v>
+        <v>79373</v>
       </c>
       <c r="BI30" s="6">
-        <v>332271</v>
+        <v>335298</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.96872294088320954</v>
+        <v>0.97754803949865743</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5745,14 +5745,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>19243</v>
+        <v>19256</v>
       </c>
       <c r="F31" s="13">
-        <v>83583</v>
+        <v>83596</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>1.0084456402398563</v>
+        <v>1.0086024878443107</v>
       </c>
       <c r="H31" s="7">
         <v>85478</v>
@@ -5762,14 +5762,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>18026</v>
+        <v>18037</v>
       </c>
       <c r="K31" s="13">
-        <v>85113</v>
+        <v>85124</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.99572989541168488</v>
+        <v>0.99585858349516831</v>
       </c>
       <c r="M31" s="7">
         <v>149930</v>
@@ -5779,14 +5779,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>38861</v>
+        <v>38915</v>
       </c>
       <c r="P31" s="13">
-        <v>150713</v>
+        <v>150767</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>1.0052224371373308</v>
+        <v>1.0055826052157673</v>
       </c>
       <c r="R31" s="7">
         <v>83981</v>
@@ -5796,14 +5796,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>18556</v>
+        <v>18578</v>
       </c>
       <c r="U31" s="13">
-        <v>84365</v>
+        <v>84387</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>1.0045724628189709</v>
+        <v>1.0048344268346412</v>
       </c>
       <c r="W31" s="7">
         <v>85994</v>
@@ -5813,14 +5813,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>18967</v>
+        <v>18997</v>
       </c>
       <c r="Z31" s="13">
-        <v>85531</v>
+        <v>85561</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.99461590343512341</v>
+        <v>0.99496476498360353</v>
       </c>
       <c r="AB31" s="7">
         <v>153633</v>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>40168</v>
+        <v>40261</v>
       </c>
       <c r="AE31" s="13">
-        <v>153409</v>
+        <v>153502</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>0.99854197991316973</v>
+        <v>0.99914731860993411</v>
       </c>
       <c r="AG31" s="7">
         <v>85109</v>
@@ -5847,14 +5847,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>20250</v>
+        <v>20289</v>
       </c>
       <c r="AJ31" s="13">
-        <v>85768</v>
+        <v>85807</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>1.007743011902384</v>
+        <v>1.0082012478116298</v>
       </c>
       <c r="AL31" s="7">
         <v>88549</v>
@@ -5864,14 +5864,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>18205</v>
+        <v>18256</v>
       </c>
       <c r="AO31" s="13">
-        <v>88376</v>
+        <v>88427</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.99804627946108937</v>
+        <v>0.99862223175868725</v>
       </c>
       <c r="AQ31" s="7">
         <v>156407</v>
@@ -5881,14 +5881,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>34071</v>
+        <v>34286</v>
       </c>
       <c r="AT31" s="13">
-        <v>157194</v>
+        <v>157409</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>1.0050317441035248</v>
+        <v>1.0064063628865716</v>
       </c>
       <c r="AV31" s="7">
         <v>87916</v>
@@ -5898,14 +5898,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>17302</v>
+        <v>17436</v>
       </c>
       <c r="AY31" s="13">
-        <v>88728</v>
+        <v>88862</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>1.0092360889940397</v>
+        <v>1.0107602711679331</v>
       </c>
       <c r="BA31" s="7">
         <v>90084</v>
@@ -5915,14 +5915,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>17314</v>
+        <v>17543</v>
       </c>
       <c r="BD31" s="13">
-        <v>90072</v>
+        <v>90301</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.99986679099507125</v>
+        <v>1.0024088628391279</v>
       </c>
       <c r="BF31" s="7">
         <v>159779</v>
@@ -5932,14 +5932,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>48250</v>
+        <v>49597</v>
       </c>
       <c r="BI31" s="6">
-        <v>157544</v>
+        <v>158891</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>0.98601192897689938</v>
+        <v>0.99444232345927808</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5957,14 +5957,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>48432</v>
+        <v>48452</v>
       </c>
       <c r="F32" s="13">
-        <v>231645</v>
+        <v>231665</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.99840957873231784</v>
+        <v>0.99849578042704323</v>
       </c>
       <c r="H32" s="7">
         <v>238678</v>
@@ -5974,14 +5974,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>46578</v>
+        <v>46607</v>
       </c>
       <c r="K32" s="13">
-        <v>235850</v>
+        <v>235879</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.98815140063181361</v>
+        <v>0.98827290324202477</v>
       </c>
       <c r="M32" s="7">
         <v>498323</v>
@@ -5991,14 +5991,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>108026</v>
+        <v>108122</v>
       </c>
       <c r="P32" s="13">
-        <v>494702</v>
+        <v>494798</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.99273362859029179</v>
+        <v>0.99292627472542905</v>
       </c>
       <c r="R32" s="7">
         <v>234167</v>
@@ -6008,14 +6008,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>43939</v>
+        <v>43976</v>
       </c>
       <c r="U32" s="13">
-        <v>233726</v>
+        <v>233763</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.99811672865946099</v>
+        <v>0.99827473555197788</v>
       </c>
       <c r="W32" s="7">
         <v>242821</v>
@@ -6025,14 +6025,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>46234</v>
+        <v>46291</v>
       </c>
       <c r="Z32" s="13">
-        <v>238196</v>
+        <v>238253</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.98095304771827807</v>
+        <v>0.98118778853558797</v>
       </c>
       <c r="AB32" s="7">
         <v>507064</v>
@@ -6042,14 +6042,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>111260</v>
+        <v>111457</v>
       </c>
       <c r="AE32" s="13">
-        <v>503768</v>
+        <v>503965</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.99349983434043831</v>
+        <v>0.99388834545540605</v>
       </c>
       <c r="AG32" s="7">
         <v>238186</v>
@@ -6059,14 +6059,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>47780</v>
+        <v>47880</v>
       </c>
       <c r="AJ32" s="13">
-        <v>237913</v>
+        <v>238013</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.99885383691736707</v>
+        <v>0.99927367687437552</v>
       </c>
       <c r="AL32" s="7">
         <v>247675</v>
@@ -6076,14 +6076,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>43734</v>
+        <v>43891</v>
       </c>
       <c r="AO32" s="13">
-        <v>247347</v>
+        <v>247504</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.99867568385989702</v>
+        <v>0.99930957908549511</v>
       </c>
       <c r="AQ32" s="7">
         <v>518099</v>
@@ -6093,14 +6093,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>100872</v>
+        <v>101464</v>
       </c>
       <c r="AT32" s="13">
-        <v>517698</v>
+        <v>518290</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.99922601664932764</v>
+        <v>1.0003686554114175</v>
       </c>
       <c r="AV32" s="7">
         <v>246693</v>
@@ -6110,14 +6110,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>43335</v>
+        <v>43679</v>
       </c>
       <c r="AY32" s="13">
-        <v>248171</v>
+        <v>248515</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>1.005991252285229</v>
+        <v>1.0073856980133202</v>
       </c>
       <c r="BA32" s="7">
         <v>255610</v>
@@ -6127,14 +6127,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>41160</v>
+        <v>41708</v>
       </c>
       <c r="BD32" s="13">
-        <v>254279</v>
+        <v>254827</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.99479284848010641</v>
+        <v>0.99693673956417983</v>
       </c>
       <c r="BF32" s="7">
         <v>535637</v>
@@ -6144,14 +6144,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>127049</v>
+        <v>130229</v>
       </c>
       <c r="BI32" s="6">
-        <v>525692</v>
+        <v>528872</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.9814333214471741</v>
+        <v>0.98737017793767046</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6169,14 +6169,14 @@
       </c>
       <c r="E33" s="20">
         <f t="shared" si="0"/>
-        <v>81470</v>
+        <v>81488</v>
       </c>
       <c r="F33" s="13">
-        <v>718686</v>
+        <v>718704</v>
       </c>
       <c r="G33" s="21">
         <f t="shared" si="1"/>
-        <v>1.004041671265296</v>
+        <v>1.0040668182002339</v>
       </c>
       <c r="H33" s="7">
         <v>726544</v>
@@ -6186,14 +6186,14 @@
       </c>
       <c r="J33" s="20">
         <f t="shared" si="2"/>
-        <v>73256</v>
+        <v>73282</v>
       </c>
       <c r="K33" s="13">
-        <v>729989</v>
+        <v>730015</v>
       </c>
       <c r="L33" s="21">
         <f t="shared" si="3"/>
-        <v>1.0047416261093616</v>
+        <v>1.0047774119667907</v>
       </c>
       <c r="M33" s="7">
         <v>1152516</v>
@@ -6203,14 +6203,14 @@
       </c>
       <c r="O33" s="20">
         <f t="shared" si="4"/>
-        <v>140340</v>
+        <v>140400</v>
       </c>
       <c r="P33" s="13">
-        <v>1154267</v>
+        <v>1154327</v>
       </c>
       <c r="Q33" s="21">
         <f t="shared" si="5"/>
-        <v>1.0015192847648102</v>
+        <v>1.0015713447795953</v>
       </c>
       <c r="R33" s="7">
         <v>733468</v>
@@ -6220,14 +6220,14 @@
       </c>
       <c r="T33" s="20">
         <f t="shared" si="6"/>
-        <v>83131</v>
+        <v>83172</v>
       </c>
       <c r="U33" s="13">
-        <v>737256</v>
+        <v>737297</v>
       </c>
       <c r="V33" s="21">
         <f t="shared" si="7"/>
-        <v>1.0051645061543244</v>
+        <v>1.0052204049801763</v>
       </c>
       <c r="W33" s="7">
         <v>745690</v>
@@ -6237,14 +6237,14 @@
       </c>
       <c r="Y33" s="20">
         <f t="shared" si="8"/>
-        <v>81023</v>
+        <v>81079</v>
       </c>
       <c r="Z33" s="13">
-        <v>746575</v>
+        <v>746631</v>
       </c>
       <c r="AA33" s="21">
         <f t="shared" si="9"/>
-        <v>1.0011868202604299</v>
+        <v>1.0012619184915983</v>
       </c>
       <c r="AB33" s="7">
         <v>1180887</v>
@@ -6254,14 +6254,14 @@
       </c>
       <c r="AD33" s="20">
         <f t="shared" si="10"/>
-        <v>140918</v>
+        <v>141053</v>
       </c>
       <c r="AE33" s="13">
-        <v>1180803</v>
+        <v>1180938</v>
       </c>
       <c r="AF33" s="21">
         <f t="shared" si="11"/>
-        <v>0.99992886702961414</v>
+        <v>1.000043187874877</v>
       </c>
       <c r="AG33" s="7">
         <v>749948</v>
@@ -6271,14 +6271,14 @@
       </c>
       <c r="AI33" s="20">
         <f t="shared" si="12"/>
-        <v>81219</v>
+        <v>81317</v>
       </c>
       <c r="AJ33" s="13">
-        <v>751705</v>
+        <v>751803</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="13"/>
-        <v>1.0023428291028178</v>
+        <v>1.0024735048296682</v>
       </c>
       <c r="AL33" s="7">
         <v>765123</v>
@@ -6288,14 +6288,14 @@
       </c>
       <c r="AN33" s="20">
         <f t="shared" si="14"/>
-        <v>75702</v>
+        <v>75864</v>
       </c>
       <c r="AO33" s="13">
-        <v>774173</v>
+        <v>774335</v>
       </c>
       <c r="AP33" s="21">
         <f t="shared" si="15"/>
-        <v>1.0118281635763138</v>
+        <v>1.0120398942392268</v>
       </c>
       <c r="AQ33" s="7">
         <v>1217820</v>
@@ -6305,14 +6305,14 @@
       </c>
       <c r="AS33" s="20">
         <f t="shared" si="16"/>
-        <v>139769</v>
+        <v>140244</v>
       </c>
       <c r="AT33" s="13">
-        <v>1223595</v>
+        <v>1224070</v>
       </c>
       <c r="AU33" s="21">
         <f t="shared" si="17"/>
-        <v>1.004742080110361</v>
+        <v>1.0051321213315596</v>
       </c>
       <c r="AV33" s="7">
         <v>779865</v>
@@ -6322,14 +6322,14 @@
       </c>
       <c r="AX33" s="20">
         <f t="shared" si="18"/>
-        <v>73070</v>
+        <v>73542</v>
       </c>
       <c r="AY33" s="13">
-        <v>785599</v>
+        <v>786071</v>
       </c>
       <c r="AZ33" s="21">
         <f t="shared" si="19"/>
-        <v>1.0073525546088105</v>
+        <v>1.0079577875657966</v>
       </c>
       <c r="BA33" s="7">
         <v>794982</v>
@@ -6339,14 +6339,14 @@
       </c>
       <c r="BC33" s="20">
         <f t="shared" si="20"/>
-        <v>74577</v>
+        <v>75414</v>
       </c>
       <c r="BD33" s="13">
-        <v>799407</v>
+        <v>800244</v>
       </c>
       <c r="BE33" s="21">
         <f t="shared" si="21"/>
-        <v>1.0055661637621984</v>
+        <v>1.0066190177890819</v>
       </c>
       <c r="BF33" s="7">
         <v>1258934</v>
@@ -6356,14 +6356,14 @@
       </c>
       <c r="BH33" s="20">
         <f t="shared" si="22"/>
-        <v>163662</v>
+        <v>167383</v>
       </c>
       <c r="BI33" s="6">
-        <v>1253850</v>
+        <v>1257571</v>
       </c>
       <c r="BJ33" s="21">
         <f t="shared" si="23"/>
-        <v>0.99596166280361009</v>
+        <v>0.99891733800183324</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6569,14 +6569,14 @@
       </c>
       <c r="E35" s="4">
         <f t="shared" ref="E35:E48" si="24">F35-D35</f>
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="F35" s="13">
-        <v>12241</v>
+        <v>12243</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" ref="G35:G48" si="25">F35/C35</f>
-        <v>0.99861315059552946</v>
+        <v>0.99877630934899653</v>
       </c>
       <c r="H35" s="7">
         <v>12343</v>
@@ -6586,14 +6586,14 @@
       </c>
       <c r="J35" s="4">
         <f t="shared" ref="J35:J48" si="26">K35-I35</f>
-        <v>2180</v>
+        <v>2184</v>
       </c>
       <c r="K35" s="13">
-        <v>12329</v>
+        <v>12333</v>
       </c>
       <c r="L35" s="5">
         <f t="shared" ref="L35:L48" si="27">K35/H35</f>
-        <v>0.99886575386858945</v>
+        <v>0.99918982419184965</v>
       </c>
       <c r="M35" s="7">
         <v>15097</v>
@@ -6603,14 +6603,14 @@
       </c>
       <c r="O35" s="4">
         <f t="shared" ref="O35:O48" si="28">P35-N35</f>
-        <v>2853</v>
+        <v>2856</v>
       </c>
       <c r="P35" s="13">
-        <v>15067</v>
+        <v>15070</v>
       </c>
       <c r="Q35" s="5">
         <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
-        <v>0.99801285023514608</v>
+        <v>0.99821156521163146</v>
       </c>
       <c r="R35" s="7">
         <v>12455</v>
@@ -6620,14 +6620,14 @@
       </c>
       <c r="T35" s="4">
         <f t="shared" ref="T35:T48" si="30">U35-S35</f>
-        <v>2291</v>
+        <v>2294</v>
       </c>
       <c r="U35" s="13">
-        <v>12401</v>
+        <v>12404</v>
       </c>
       <c r="V35" s="5">
         <f t="shared" ref="V35:V48" si="31">U35/R35</f>
-        <v>0.99566439181051791</v>
+        <v>0.99590525893215576</v>
       </c>
       <c r="W35" s="7">
         <v>12547</v>
@@ -6637,14 +6637,14 @@
       </c>
       <c r="Y35" s="4">
         <f t="shared" ref="Y35:Y48" si="32">Z35-X35</f>
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="Z35" s="13">
-        <v>12438</v>
+        <v>12440</v>
       </c>
       <c r="AA35" s="5">
         <f t="shared" ref="AA35:AA48" si="33">Z35/W35</f>
-        <v>0.991312664381924</v>
+        <v>0.9914720650354667</v>
       </c>
       <c r="AB35" s="7">
         <v>15257</v>
@@ -6654,14 +6654,14 @@
       </c>
       <c r="AD35" s="4">
         <f t="shared" ref="AD35:AD48" si="34">AE35-AC35</f>
-        <v>2703</v>
+        <v>2709</v>
       </c>
       <c r="AE35" s="13">
-        <v>15178</v>
+        <v>15184</v>
       </c>
       <c r="AF35" s="5">
         <f t="shared" ref="AF35:AF48" si="35">AE35/AB35</f>
-        <v>0.9948220488955889</v>
+        <v>0.99521531100478466</v>
       </c>
       <c r="AG35" s="7">
         <v>12574</v>
@@ -6671,14 +6671,14 @@
       </c>
       <c r="AI35" s="4">
         <f t="shared" ref="AI35:AI48" si="36">AJ35-AH35</f>
-        <v>2193</v>
+        <v>2197</v>
       </c>
       <c r="AJ35" s="13">
-        <v>12516</v>
+        <v>12520</v>
       </c>
       <c r="AK35" s="5">
         <f t="shared" ref="AK35:AK48" si="37">AJ35/AG35</f>
-        <v>0.99538730714172097</v>
+        <v>0.99570542389056782</v>
       </c>
       <c r="AL35" s="7">
         <v>12702</v>
@@ -6688,14 +6688,14 @@
       </c>
       <c r="AN35" s="4">
         <f t="shared" ref="AN35:AN48" si="38">AO35-AM35</f>
-        <v>2093</v>
+        <v>2102</v>
       </c>
       <c r="AO35" s="13">
-        <v>12617</v>
+        <v>12626</v>
       </c>
       <c r="AP35" s="5">
         <f t="shared" ref="AP35:AP48" si="39">AO35/AL35</f>
-        <v>0.99330814045032279</v>
+        <v>0.99401669028499451</v>
       </c>
       <c r="AQ35" s="7">
         <v>15458</v>
@@ -6705,14 +6705,14 @@
       </c>
       <c r="AS35" s="4">
         <f t="shared" ref="AS35:AS48" si="40">AT35-AR35</f>
-        <v>2657</v>
+        <v>2678</v>
       </c>
       <c r="AT35" s="13">
-        <v>15375</v>
+        <v>15396</v>
       </c>
       <c r="AU35" s="5">
         <f t="shared" ref="AU35:AU48" si="41">AT35/AQ35</f>
-        <v>0.99463061198085134</v>
+        <v>0.99598913184111781</v>
       </c>
       <c r="AV35" s="7">
         <v>12806</v>
@@ -6722,14 +6722,14 @@
       </c>
       <c r="AX35" s="4">
         <f t="shared" ref="AX35:AX48" si="42">AY35-AW35</f>
-        <v>1997</v>
+        <v>2019</v>
       </c>
       <c r="AY35" s="13">
-        <v>12685</v>
+        <v>12707</v>
       </c>
       <c r="AZ35" s="5">
         <f t="shared" ref="AZ35:AZ48" si="43">AY35/AV35</f>
-        <v>0.99055130407621428</v>
+        <v>0.99226924878962985</v>
       </c>
       <c r="BA35" s="7">
         <v>12915</v>
@@ -6739,14 +6739,14 @@
       </c>
       <c r="BC35" s="4">
         <f t="shared" ref="BC35:BC48" si="44">BD35-BB35</f>
-        <v>1978</v>
+        <v>2013</v>
       </c>
       <c r="BD35" s="13">
-        <v>12736</v>
+        <v>12771</v>
       </c>
       <c r="BE35" s="5">
         <f t="shared" ref="BE35:BE48" si="45">BD35/BA35</f>
-        <v>0.98614014711575693</v>
+        <v>0.98885017421602783</v>
       </c>
       <c r="BF35" s="7">
         <v>15661</v>
@@ -6756,14 +6756,14 @@
       </c>
       <c r="BH35" s="4">
         <f t="shared" ref="BH35:BH48" si="46">BI35-BG35</f>
-        <v>2751</v>
+        <v>2833</v>
       </c>
       <c r="BI35" s="6">
-        <v>15350</v>
+        <v>15432</v>
       </c>
       <c r="BJ35" s="5">
         <f t="shared" ref="BJ35:BJ48" si="47">BI35/BF35</f>
-        <v>0.98014175340016607</v>
+        <v>0.98537768980269458</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6781,14 +6781,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="24"/>
-        <v>185958</v>
+        <v>186078</v>
       </c>
       <c r="F36" s="13">
-        <v>956136</v>
+        <v>956256</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="25"/>
-        <v>1.0034907274272939</v>
+        <v>1.0036166706898542</v>
       </c>
       <c r="H36" s="7">
         <v>975466</v>
@@ -6798,14 +6798,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="26"/>
-        <v>176329</v>
+        <v>176472</v>
       </c>
       <c r="K36" s="13">
-        <v>971549</v>
+        <v>971692</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="27"/>
-        <v>0.99598448331361622</v>
+        <v>0.99613107991462546</v>
       </c>
       <c r="M36" s="7">
         <v>1668278</v>
@@ -6815,14 +6815,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="28"/>
-        <v>346306</v>
+        <v>346596</v>
       </c>
       <c r="P36" s="13">
-        <v>1668379</v>
+        <v>1668669</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="29"/>
-        <v>1.0000605414685082</v>
+        <v>1.0002343734077894</v>
       </c>
       <c r="R36" s="7">
         <v>976879</v>
@@ -6832,14 +6832,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="30"/>
-        <v>185414</v>
+        <v>185600</v>
       </c>
       <c r="U36" s="13">
-        <v>977456</v>
+        <v>977642</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="31"/>
-        <v>1.000590656570568</v>
+        <v>1.000781058861947</v>
       </c>
       <c r="W36" s="7">
         <v>1000117</v>
@@ -6849,14 +6849,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="32"/>
-        <v>181412</v>
+        <v>181637</v>
       </c>
       <c r="Z36" s="13">
-        <v>989235</v>
+        <v>989460</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="33"/>
-        <v>0.98911927304505376</v>
+        <v>0.98934424672313337</v>
       </c>
       <c r="AB36" s="7">
         <v>1701420</v>
@@ -6866,14 +6866,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="34"/>
-        <v>336730</v>
+        <v>337244</v>
       </c>
       <c r="AE36" s="13">
-        <v>1697624</v>
+        <v>1698138</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="35"/>
-        <v>0.9977689224295001</v>
+        <v>0.9980710230278238</v>
       </c>
       <c r="AG36" s="7">
         <v>996655</v>
@@ -6883,14 +6883,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="36"/>
-        <v>186482</v>
+        <v>186851</v>
       </c>
       <c r="AJ36" s="13">
-        <v>997108</v>
+        <v>997477</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="37"/>
-        <v>1.0004545203706399</v>
+        <v>1.0008247588182471</v>
       </c>
       <c r="AL36" s="7">
         <v>1027093</v>
@@ -6900,14 +6900,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="38"/>
-        <v>177976</v>
+        <v>178519</v>
       </c>
       <c r="AO36" s="13">
-        <v>1032695</v>
+        <v>1033238</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="39"/>
-        <v>1.0054542285849479</v>
+        <v>1.0059829051507507</v>
       </c>
       <c r="AQ36" s="7">
         <v>1750886</v>
@@ -6917,14 +6917,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="40"/>
-        <v>321310</v>
+        <v>322894</v>
       </c>
       <c r="AT36" s="13">
-        <v>1762688</v>
+        <v>1764272</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="41"/>
-        <v>1.0067405873369255</v>
+        <v>1.0076452721650639</v>
       </c>
       <c r="AV36" s="7">
         <v>1041088</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="42"/>
-        <v>167138</v>
+        <v>168619</v>
       </c>
       <c r="AY36" s="13">
-        <v>1049138</v>
+        <v>1050619</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="43"/>
-        <v>1.0077322954447654</v>
+        <v>1.0091548456998831</v>
       </c>
       <c r="BA36" s="7">
         <v>1070068</v>
@@ -6951,14 +6951,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="44"/>
-        <v>172271</v>
+        <v>174740</v>
       </c>
       <c r="BD36" s="13">
-        <v>1068688</v>
+        <v>1071157</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="45"/>
-        <v>0.99871036233211352</v>
+        <v>1.0010176923335714</v>
       </c>
       <c r="BF36" s="7">
         <v>1814069</v>
@@ -6968,14 +6968,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="46"/>
-        <v>358503</v>
+        <v>371120</v>
       </c>
       <c r="BI36" s="6">
-        <v>1786260</v>
+        <v>1798877</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="47"/>
-        <v>0.98467037361864407</v>
+        <v>0.99162545636356725</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6993,14 +6993,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="24"/>
-        <v>146600</v>
+        <v>146712</v>
       </c>
       <c r="F37" s="13">
-        <v>734670</v>
+        <v>734782</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="25"/>
-        <v>0.99083170143553057</v>
+        <v>0.99098275313297401</v>
       </c>
       <c r="H37" s="7">
         <v>747767</v>
@@ -7010,14 +7010,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="26"/>
-        <v>140353</v>
+        <v>140494</v>
       </c>
       <c r="K37" s="13">
-        <v>739375</v>
+        <v>739516</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="27"/>
-        <v>0.9887772528073584</v>
+        <v>0.98896581421753038</v>
       </c>
       <c r="M37" s="7">
         <v>922163</v>
@@ -7027,14 +7027,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="28"/>
-        <v>188418</v>
+        <v>188647</v>
       </c>
       <c r="P37" s="13">
-        <v>913956</v>
+        <v>914185</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="29"/>
-        <v>0.99110027186083149</v>
+        <v>0.99134860106076694</v>
       </c>
       <c r="R37" s="7">
         <v>751356</v>
@@ -7044,14 +7044,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="30"/>
-        <v>140165</v>
+        <v>140409</v>
       </c>
       <c r="U37" s="13">
-        <v>744609</v>
+        <v>744853</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="31"/>
-        <v>0.99102023541437079</v>
+        <v>0.99134498160658857</v>
       </c>
       <c r="W37" s="7">
         <v>760191</v>
@@ -7061,14 +7061,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="32"/>
-        <v>138516</v>
+        <v>138820</v>
       </c>
       <c r="Z37" s="13">
-        <v>750068</v>
+        <v>750372</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="33"/>
-        <v>0.98668360977701652</v>
+        <v>0.98708350927595823</v>
       </c>
       <c r="AB37" s="7">
         <v>938023</v>
@@ -7078,14 +7078,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="34"/>
-        <v>160880</v>
+        <v>161368</v>
       </c>
       <c r="AE37" s="13">
-        <v>928254</v>
+        <v>928742</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="35"/>
-        <v>0.98958554321162706</v>
+        <v>0.99010578631867241</v>
       </c>
       <c r="AG37" s="7">
         <v>763648</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="36"/>
-        <v>142723</v>
+        <v>143254</v>
       </c>
       <c r="AJ37" s="13">
-        <v>755932</v>
+        <v>756463</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="37"/>
-        <v>0.98989586825343612</v>
+        <v>0.99059121480053636</v>
       </c>
       <c r="AL37" s="7">
         <v>773685</v>
@@ -7112,14 +7112,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="38"/>
-        <v>133525</v>
+        <v>134295</v>
       </c>
       <c r="AO37" s="13">
-        <v>768789</v>
+        <v>769559</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="39"/>
-        <v>0.99367184319199675</v>
+        <v>0.99466708027168682</v>
       </c>
       <c r="AQ37" s="7">
         <v>957323</v>
@@ -7129,14 +7129,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="40"/>
-        <v>166723</v>
+        <v>168335</v>
       </c>
       <c r="AT37" s="13">
-        <v>950186</v>
+        <v>951798</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="41"/>
-        <v>0.99254483596445509</v>
+        <v>0.9942286981509898</v>
       </c>
       <c r="AV37" s="7">
         <v>783693</v>
@@ -7146,14 +7146,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="42"/>
-        <v>125979</v>
+        <v>127906</v>
       </c>
       <c r="AY37" s="13">
-        <v>776771</v>
+        <v>778698</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="43"/>
-        <v>0.99116745970679843</v>
+        <v>0.99362633071878914</v>
       </c>
       <c r="BA37" s="7">
         <v>794943</v>
@@ -7163,14 +7163,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="44"/>
-        <v>137818</v>
+        <v>141008</v>
       </c>
       <c r="BD37" s="13">
-        <v>781478</v>
+        <v>784668</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="45"/>
-        <v>0.9830616786360783</v>
+        <v>0.98707454496737501</v>
       </c>
       <c r="BF37" s="7">
         <v>980352</v>
@@ -7180,14 +7180,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="46"/>
-        <v>196511</v>
+        <v>203771</v>
       </c>
       <c r="BI37" s="6">
-        <v>952942</v>
+        <v>960202</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="47"/>
-        <v>0.97204065478521995</v>
+        <v>0.97944615811463642</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7205,14 +7205,14 @@
       </c>
       <c r="E38" s="4">
         <f t="shared" si="24"/>
-        <v>6597</v>
+        <v>6609</v>
       </c>
       <c r="F38" s="13">
-        <v>26185</v>
+        <v>26197</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="25"/>
-        <v>1.004719515002686</v>
+        <v>1.0051799554907528</v>
       </c>
       <c r="H38" s="7">
         <v>26657</v>
@@ -7222,14 +7222,14 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" si="26"/>
-        <v>6260</v>
+        <v>6272</v>
       </c>
       <c r="K38" s="13">
-        <v>26499</v>
+        <v>26511</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="27"/>
-        <v>0.99407285140863566</v>
+        <v>0.99452301459278991</v>
       </c>
       <c r="M38" s="7">
         <v>40003</v>
@@ -7239,14 +7239,14 @@
       </c>
       <c r="O38" s="4">
         <f t="shared" si="28"/>
-        <v>9894</v>
+        <v>9916</v>
       </c>
       <c r="P38" s="13">
-        <v>40025</v>
+        <v>40047</v>
       </c>
       <c r="Q38" s="5">
         <f t="shared" si="29"/>
-        <v>1.0005499587530935</v>
+        <v>1.001099917506187</v>
       </c>
       <c r="R38" s="7">
         <v>26603</v>
@@ -7256,14 +7256,14 @@
       </c>
       <c r="T38" s="4">
         <f t="shared" si="30"/>
-        <v>6141</v>
+        <v>6161</v>
       </c>
       <c r="U38" s="13">
-        <v>26636</v>
+        <v>26656</v>
       </c>
       <c r="V38" s="5">
         <f t="shared" si="31"/>
-        <v>1.0012404616020749</v>
+        <v>1.0019922565124235</v>
       </c>
       <c r="W38" s="7">
         <v>27177</v>
@@ -7273,14 +7273,14 @@
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="32"/>
-        <v>6202</v>
+        <v>6223</v>
       </c>
       <c r="Z38" s="13">
-        <v>26887</v>
+        <v>26908</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="33"/>
-        <v>0.98932921220149395</v>
+        <v>0.99010192442138578</v>
       </c>
       <c r="AB38" s="7">
         <v>40627</v>
@@ -7290,14 +7290,14 @@
       </c>
       <c r="AD38" s="4">
         <f t="shared" si="34"/>
-        <v>8785</v>
+        <v>8821</v>
       </c>
       <c r="AE38" s="13">
-        <v>40614</v>
+        <v>40650</v>
       </c>
       <c r="AF38" s="5">
         <f t="shared" si="35"/>
-        <v>0.99968001575307064</v>
+        <v>1.0005661259753367</v>
       </c>
       <c r="AG38" s="7">
         <v>26952</v>
@@ -7307,14 +7307,14 @@
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="36"/>
-        <v>6128</v>
+        <v>6163</v>
       </c>
       <c r="AJ38" s="13">
-        <v>27030</v>
+        <v>27065</v>
       </c>
       <c r="AK38" s="5">
         <f t="shared" si="37"/>
-        <v>1.0028940338379342</v>
+        <v>1.0041926387652123</v>
       </c>
       <c r="AL38" s="7">
         <v>27600</v>
@@ -7324,14 +7324,14 @@
       </c>
       <c r="AN38" s="4">
         <f t="shared" si="38"/>
-        <v>6400</v>
+        <v>6451</v>
       </c>
       <c r="AO38" s="13">
-        <v>27553</v>
+        <v>27604</v>
       </c>
       <c r="AP38" s="5">
         <f t="shared" si="39"/>
-        <v>0.99829710144927541</v>
+        <v>1.000144927536232</v>
       </c>
       <c r="AQ38" s="7">
         <v>41434</v>
@@ -7341,14 +7341,14 @@
       </c>
       <c r="AS38" s="4">
         <f t="shared" si="40"/>
-        <v>8992</v>
+        <v>9097</v>
       </c>
       <c r="AT38" s="13">
-        <v>41566</v>
+        <v>41671</v>
       </c>
       <c r="AU38" s="5">
         <f t="shared" si="41"/>
-        <v>1.0031857894482792</v>
+        <v>1.0057199401457739</v>
       </c>
       <c r="AV38" s="7">
         <v>27593</v>
@@ -7358,14 +7358,14 @@
       </c>
       <c r="AX38" s="4">
         <f t="shared" si="42"/>
-        <v>5277</v>
+        <v>5399</v>
       </c>
       <c r="AY38" s="13">
-        <v>27633</v>
+        <v>27755</v>
       </c>
       <c r="AZ38" s="5">
         <f t="shared" si="43"/>
-        <v>1.001449643025405</v>
+        <v>1.0058710542528901</v>
       </c>
       <c r="BA38" s="7">
         <v>28279</v>
@@ -7375,14 +7375,14 @@
       </c>
       <c r="BC38" s="4">
         <f t="shared" si="44"/>
-        <v>5516</v>
+        <v>5711</v>
       </c>
       <c r="BD38" s="13">
-        <v>27794</v>
+        <v>27989</v>
       </c>
       <c r="BE38" s="5">
         <f t="shared" si="45"/>
-        <v>0.98284946426677045</v>
+        <v>0.98974504048940914</v>
       </c>
       <c r="BF38" s="7">
         <v>42642</v>
@@ -7392,14 +7392,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="46"/>
-        <v>9663</v>
+        <v>10202</v>
       </c>
       <c r="BI38" s="6">
-        <v>41174</v>
+        <v>41713</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="47"/>
-        <v>0.96557384738051688</v>
+        <v>0.97821396744993194</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7417,14 +7417,14 @@
       </c>
       <c r="E39" s="4">
         <f t="shared" si="24"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F39" s="13">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="25"/>
-        <v>0.99609375</v>
+        <v>1</v>
       </c>
       <c r="H39" s="7">
         <v>262</v>
@@ -7468,14 +7468,14 @@
       </c>
       <c r="T39" s="4">
         <f t="shared" si="30"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U39" s="13">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V39" s="5">
         <f t="shared" si="31"/>
-        <v>0.95454545454545459</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="W39" s="7">
         <v>265</v>
@@ -7485,14 +7485,14 @@
       </c>
       <c r="Y39" s="4">
         <f t="shared" si="32"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z39" s="13">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA39" s="5">
         <f t="shared" si="33"/>
-        <v>0.96226415094339623</v>
+        <v>0.96603773584905661</v>
       </c>
       <c r="AB39" s="7">
         <v>322</v>
@@ -7502,14 +7502,14 @@
       </c>
       <c r="AD39" s="4">
         <f t="shared" si="34"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AE39" s="13">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AF39" s="5">
         <f t="shared" si="35"/>
-        <v>0.96583850931677018</v>
+        <v>0.96894409937888204</v>
       </c>
       <c r="AG39" s="7">
         <v>267</v>
@@ -7519,14 +7519,14 @@
       </c>
       <c r="AI39" s="4">
         <f t="shared" si="36"/>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AJ39" s="13">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AK39" s="5">
         <f t="shared" si="37"/>
-        <v>0.94756554307116103</v>
+        <v>0.9550561797752809</v>
       </c>
       <c r="AL39" s="7">
         <v>276</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="AN39" s="4">
         <f t="shared" si="38"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO39" s="13">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AP39" s="5">
         <f t="shared" si="39"/>
-        <v>0.94927536231884058</v>
+        <v>0.95289855072463769</v>
       </c>
       <c r="AQ39" s="7">
         <v>338</v>
@@ -7553,14 +7553,14 @@
       </c>
       <c r="AS39" s="4">
         <f t="shared" si="40"/>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AT39" s="13">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AU39" s="5">
         <f t="shared" si="41"/>
-        <v>0.94970414201183428</v>
+        <v>0.95562130177514792</v>
       </c>
       <c r="AV39" s="7">
         <v>279</v>
@@ -7570,14 +7570,14 @@
       </c>
       <c r="AX39" s="4">
         <f t="shared" si="42"/>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AY39" s="13">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AZ39" s="5">
         <f t="shared" si="43"/>
-        <v>0.94982078853046592</v>
+        <v>0.96415770609318996</v>
       </c>
       <c r="BA39" s="7">
         <v>291</v>
@@ -7587,14 +7587,14 @@
       </c>
       <c r="BC39" s="4">
         <f t="shared" si="44"/>
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="BD39" s="13">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="BE39" s="5">
         <f t="shared" si="45"/>
-        <v>0.92783505154639179</v>
+        <v>0.94158075601374569</v>
       </c>
       <c r="BF39" s="7">
         <v>344</v>
@@ -7604,14 +7604,14 @@
       </c>
       <c r="BH39" s="4">
         <f t="shared" si="46"/>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="BI39" s="6">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="BJ39" s="5">
         <f t="shared" si="47"/>
-        <v>0.96220930232558144</v>
+        <v>0.97383720930232553</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.3">
@@ -7629,14 +7629,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="24"/>
-        <v>73454</v>
+        <v>73504</v>
       </c>
       <c r="F40" s="13">
-        <v>301369</v>
+        <v>301419</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="25"/>
-        <v>0.99169118179365179</v>
+        <v>0.99185571284724283</v>
       </c>
       <c r="H40" s="7">
         <v>306465</v>
@@ -7646,14 +7646,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="26"/>
-        <v>71265</v>
+        <v>71330</v>
       </c>
       <c r="K40" s="13">
-        <v>302725</v>
+        <v>302790</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="27"/>
-        <v>0.98779632258169769</v>
+        <v>0.98800841857960942</v>
       </c>
       <c r="M40" s="7">
         <v>361770</v>
@@ -7663,14 +7663,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="28"/>
-        <v>90691</v>
+        <v>90788</v>
       </c>
       <c r="P40" s="13">
-        <v>358505</v>
+        <v>358602</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="29"/>
-        <v>0.99097492882217986</v>
+        <v>0.99124305497968324</v>
       </c>
       <c r="R40" s="7">
         <v>306479</v>
@@ -7680,14 +7680,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="30"/>
-        <v>70132</v>
+        <v>70237</v>
       </c>
       <c r="U40" s="13">
-        <v>304571</v>
+        <v>304676</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="31"/>
-        <v>0.99377445110431706</v>
+        <v>0.99411705206555756</v>
       </c>
       <c r="W40" s="7">
         <v>309858</v>
@@ -7697,14 +7697,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="32"/>
-        <v>70468</v>
+        <v>70598</v>
       </c>
       <c r="Z40" s="13">
-        <v>306082</v>
+        <v>306212</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="33"/>
-        <v>0.9878137727604257</v>
+        <v>0.98823331977873741</v>
       </c>
       <c r="AB40" s="7">
         <v>365821</v>
@@ -7714,14 +7714,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="34"/>
-        <v>65756</v>
+        <v>65942</v>
       </c>
       <c r="AE40" s="13">
-        <v>362541</v>
+        <v>362727</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="35"/>
-        <v>0.9910338662897975</v>
+        <v>0.99154231167702234</v>
       </c>
       <c r="AG40" s="7">
         <v>311342</v>
@@ -7731,14 +7731,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="36"/>
-        <v>72835</v>
+        <v>73050</v>
       </c>
       <c r="AJ40" s="13">
-        <v>308775</v>
+        <v>308990</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="37"/>
-        <v>0.99175504750403098</v>
+        <v>0.9924456064392212</v>
       </c>
       <c r="AL40" s="7">
         <v>314792</v>
@@ -7748,14 +7748,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="38"/>
-        <v>70645</v>
+        <v>70975</v>
       </c>
       <c r="AO40" s="13">
-        <v>312504</v>
+        <v>312834</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="39"/>
-        <v>0.99273170855676129</v>
+        <v>0.99378001982261299</v>
       </c>
       <c r="AQ40" s="7">
         <v>372144</v>
@@ -7765,14 +7765,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="40"/>
-        <v>75244</v>
+        <v>75961</v>
       </c>
       <c r="AT40" s="13">
-        <v>369386</v>
+        <v>370103</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="41"/>
-        <v>0.99258889032202591</v>
+        <v>0.99451556386775009</v>
       </c>
       <c r="AV40" s="7">
         <v>317868</v>
@@ -7782,14 +7782,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="42"/>
-        <v>64776</v>
+        <v>65798</v>
       </c>
       <c r="AY40" s="13">
-        <v>314592</v>
+        <v>315614</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="43"/>
-        <v>0.98969383517686582</v>
+        <v>0.99290900625416845</v>
       </c>
       <c r="BA40" s="7">
         <v>321637</v>
@@ -7799,14 +7799,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="44"/>
-        <v>71090</v>
+        <v>72872</v>
       </c>
       <c r="BD40" s="13">
-        <v>315723</v>
+        <v>317505</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="45"/>
-        <v>0.98161281195882311</v>
+        <v>0.9871532193124547</v>
       </c>
       <c r="BF40" s="7">
         <v>380248</v>
@@ -7816,14 +7816,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="46"/>
-        <v>88481</v>
+        <v>91567</v>
       </c>
       <c r="BI40" s="6">
-        <v>368862</v>
+        <v>371948</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="47"/>
-        <v>0.97005638425448659</v>
+        <v>0.97817214028739141</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7841,14 +7841,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="24"/>
-        <v>163389</v>
+        <v>163495</v>
       </c>
       <c r="F41" s="13">
-        <v>975601</v>
+        <v>975707</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="25"/>
-        <v>0.99812570273358892</v>
+        <v>0.99823415006450567</v>
       </c>
       <c r="H41" s="7">
         <v>983280</v>
@@ -7858,14 +7858,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="26"/>
-        <v>163283</v>
+        <v>163398</v>
       </c>
       <c r="K41" s="13">
-        <v>979977</v>
+        <v>980092</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="27"/>
-        <v>0.99664083475713938</v>
+        <v>0.99675779025303068</v>
       </c>
       <c r="M41" s="7">
         <v>1084276</v>
@@ -7875,14 +7875,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="28"/>
-        <v>190584</v>
+        <v>190726</v>
       </c>
       <c r="P41" s="13">
-        <v>1081791</v>
+        <v>1081933</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="29"/>
-        <v>0.99770814810989084</v>
+        <v>0.99783911107503998</v>
       </c>
       <c r="R41" s="7">
         <v>988018</v>
@@ -7892,14 +7892,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="30"/>
-        <v>163795</v>
+        <v>163962</v>
       </c>
       <c r="U41" s="13">
-        <v>988086</v>
+        <v>988253</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="31"/>
-        <v>1.0000688246570406</v>
+        <v>1.000237849917714</v>
       </c>
       <c r="W41" s="7">
         <v>994033</v>
@@ -7909,14 +7909,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="32"/>
-        <v>161507</v>
+        <v>161697</v>
       </c>
       <c r="Z41" s="13">
-        <v>992966</v>
+        <v>993156</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="33"/>
-        <v>0.99892659499231917</v>
+        <v>0.99911773552789496</v>
       </c>
       <c r="AB41" s="7">
         <v>1097882</v>
@@ -7926,14 +7926,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="34"/>
-        <v>139801</v>
+        <v>140094</v>
       </c>
       <c r="AE41" s="13">
-        <v>1096400</v>
+        <v>1096693</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="35"/>
-        <v>0.99865012815584919</v>
+        <v>0.99891700565270225</v>
       </c>
       <c r="AG41" s="7">
         <v>1002140</v>
@@ -7943,14 +7943,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="36"/>
-        <v>156891</v>
+        <v>157208</v>
       </c>
       <c r="AJ41" s="13">
-        <v>1001595</v>
+        <v>1001912</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="37"/>
-        <v>0.9994561638094478</v>
+        <v>0.99977248687808096</v>
       </c>
       <c r="AL41" s="7">
         <v>1011306</v>
@@ -7960,14 +7960,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="38"/>
-        <v>151372</v>
+        <v>151810</v>
       </c>
       <c r="AO41" s="13">
-        <v>1014481</v>
+        <v>1014919</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="39"/>
-        <v>1.0031395047591927</v>
+        <v>1.0035726080929017</v>
       </c>
       <c r="AQ41" s="7">
         <v>1119532</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="40"/>
-        <v>187124</v>
+        <v>187963</v>
       </c>
       <c r="AT41" s="13">
-        <v>1122674</v>
+        <v>1123513</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="41"/>
-        <v>1.0028065298714106</v>
+        <v>1.0035559501648903</v>
       </c>
       <c r="AV41" s="7">
         <v>1028062</v>
@@ -7994,14 +7994,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="42"/>
-        <v>148954</v>
+        <v>150081</v>
       </c>
       <c r="AY41" s="13">
-        <v>1028662</v>
+        <v>1029789</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="43"/>
-        <v>1.0005836223885329</v>
+        <v>1.0016798597749941</v>
       </c>
       <c r="BA41" s="7">
         <v>1037044</v>
@@ -8011,14 +8011,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="44"/>
-        <v>149685</v>
+        <v>151501</v>
       </c>
       <c r="BD41" s="13">
-        <v>1035371</v>
+        <v>1037187</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="45"/>
-        <v>0.99838676083174871</v>
+        <v>1.0001378919312971</v>
       </c>
       <c r="BF41" s="7">
         <v>1143357</v>
@@ -8028,14 +8028,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="46"/>
-        <v>192424</v>
+        <v>196521</v>
       </c>
       <c r="BI41" s="6">
-        <v>1136213</v>
+        <v>1140310</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="47"/>
-        <v>0.99375173283585094</v>
+        <v>0.99733504058662348</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8053,14 +8053,14 @@
       </c>
       <c r="E42" s="4">
         <f t="shared" si="24"/>
-        <v>4277</v>
+        <v>4280</v>
       </c>
       <c r="F42" s="13">
-        <v>19568</v>
+        <v>19571</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="25"/>
-        <v>0.99451107948770079</v>
+        <v>0.99466354950193125</v>
       </c>
       <c r="H42" s="7">
         <v>19882</v>
@@ -8070,14 +8070,14 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" si="26"/>
-        <v>4307</v>
+        <v>4310</v>
       </c>
       <c r="K42" s="13">
-        <v>19665</v>
+        <v>19668</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="27"/>
-        <v>0.9890856050699125</v>
+        <v>0.98923649532240221</v>
       </c>
       <c r="M42" s="7">
         <v>21930</v>
@@ -8087,14 +8087,14 @@
       </c>
       <c r="O42" s="4">
         <f t="shared" si="28"/>
-        <v>5201</v>
+        <v>5207</v>
       </c>
       <c r="P42" s="13">
-        <v>21738</v>
+        <v>21744</v>
       </c>
       <c r="Q42" s="5">
         <f t="shared" si="29"/>
-        <v>0.99124487004103967</v>
+        <v>0.99151846785225717</v>
       </c>
       <c r="R42" s="7">
         <v>20021</v>
@@ -8104,14 +8104,14 @@
       </c>
       <c r="T42" s="4">
         <f t="shared" si="30"/>
-        <v>4371</v>
+        <v>4376</v>
       </c>
       <c r="U42" s="13">
-        <v>19807</v>
+        <v>19812</v>
       </c>
       <c r="V42" s="5">
         <f t="shared" si="31"/>
-        <v>0.98931122321562359</v>
+        <v>0.98956096099095947</v>
       </c>
       <c r="W42" s="7">
         <v>20153</v>
@@ -8121,14 +8121,14 @@
       </c>
       <c r="Y42" s="4">
         <f t="shared" si="32"/>
-        <v>4239</v>
+        <v>4245</v>
       </c>
       <c r="Z42" s="13">
-        <v>19902</v>
+        <v>19908</v>
       </c>
       <c r="AA42" s="5">
         <f t="shared" si="33"/>
-        <v>0.987545278618568</v>
+        <v>0.98784300104202849</v>
       </c>
       <c r="AB42" s="7">
         <v>22238</v>
@@ -8138,14 +8138,14 @@
       </c>
       <c r="AD42" s="4">
         <f t="shared" si="34"/>
-        <v>3888</v>
+        <v>3897</v>
       </c>
       <c r="AE42" s="13">
-        <v>22045</v>
+        <v>22054</v>
       </c>
       <c r="AF42" s="5">
         <f t="shared" si="35"/>
-        <v>0.99132116197499776</v>
+        <v>0.9917258746290134</v>
       </c>
       <c r="AG42" s="7">
         <v>20276</v>
@@ -8155,14 +8155,14 @@
       </c>
       <c r="AI42" s="4">
         <f t="shared" si="36"/>
-        <v>4336</v>
+        <v>4345</v>
       </c>
       <c r="AJ42" s="13">
-        <v>20144</v>
+        <v>20153</v>
       </c>
       <c r="AK42" s="5">
         <f t="shared" si="37"/>
-        <v>0.99348984020516862</v>
+        <v>0.9939337147366345</v>
       </c>
       <c r="AL42" s="7">
         <v>20453</v>
@@ -8172,14 +8172,14 @@
       </c>
       <c r="AN42" s="4">
         <f t="shared" si="38"/>
-        <v>3907</v>
+        <v>3916</v>
       </c>
       <c r="AO42" s="13">
-        <v>20325</v>
+        <v>20334</v>
       </c>
       <c r="AP42" s="5">
         <f t="shared" si="39"/>
-        <v>0.99374174937661952</v>
+        <v>0.99418178262357604</v>
       </c>
       <c r="AQ42" s="7">
         <v>22621</v>
@@ -8189,14 +8189,14 @@
       </c>
       <c r="AS42" s="4">
         <f t="shared" si="40"/>
-        <v>4820</v>
+        <v>4838</v>
       </c>
       <c r="AT42" s="13">
-        <v>22550</v>
+        <v>22568</v>
       </c>
       <c r="AU42" s="5">
         <f t="shared" si="41"/>
-        <v>0.99686132354891477</v>
+        <v>0.99765704433933067</v>
       </c>
       <c r="AV42" s="7">
         <v>20714</v>
@@ -8206,14 +8206,14 @@
       </c>
       <c r="AX42" s="4">
         <f t="shared" si="42"/>
-        <v>3903</v>
+        <v>3940</v>
       </c>
       <c r="AY42" s="13">
-        <v>20599</v>
+        <v>20636</v>
       </c>
       <c r="AZ42" s="5">
         <f t="shared" si="43"/>
-        <v>0.99444819928550743</v>
+        <v>0.99623443081973539</v>
       </c>
       <c r="BA42" s="7">
         <v>20927</v>
@@ -8223,14 +8223,14 @@
       </c>
       <c r="BC42" s="4">
         <f t="shared" si="44"/>
-        <v>3818</v>
+        <v>3897</v>
       </c>
       <c r="BD42" s="13">
-        <v>20686</v>
+        <v>20765</v>
       </c>
       <c r="BE42" s="5">
         <f t="shared" si="45"/>
-        <v>0.98848377693888279</v>
+        <v>0.99225880441534864</v>
       </c>
       <c r="BF42" s="7">
         <v>23165</v>
@@ -8240,14 +8240,14 @@
       </c>
       <c r="BH42" s="4">
         <f t="shared" si="46"/>
-        <v>4755</v>
+        <v>4907</v>
       </c>
       <c r="BI42" s="6">
-        <v>22702</v>
+        <v>22854</v>
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="47"/>
-        <v>0.98001295057198357</v>
+        <v>0.98657457371033885</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8265,14 +8265,14 @@
       </c>
       <c r="E43" s="4">
         <f t="shared" si="24"/>
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F43" s="13">
-        <v>3885</v>
+        <v>3887</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" si="25"/>
-        <v>0.99259070005109862</v>
+        <v>0.99310168625447115</v>
       </c>
       <c r="H43" s="7">
         <v>3941</v>
@@ -8282,14 +8282,14 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" si="26"/>
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="K43" s="13">
-        <v>3921</v>
+        <v>3924</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" si="27"/>
-        <v>0.99492514590205527</v>
+        <v>0.99568637401674698</v>
       </c>
       <c r="M43" s="7">
         <v>4896</v>
@@ -8299,14 +8299,14 @@
       </c>
       <c r="O43" s="4">
         <f t="shared" si="28"/>
-        <v>1666</v>
+        <v>1672</v>
       </c>
       <c r="P43" s="13">
-        <v>4855</v>
+        <v>4861</v>
       </c>
       <c r="Q43" s="5">
         <f t="shared" si="29"/>
-        <v>0.99162581699346408</v>
+        <v>0.99285130718954251</v>
       </c>
       <c r="R43" s="7">
         <v>3969</v>
@@ -8316,14 +8316,14 @@
       </c>
       <c r="T43" s="4">
         <f t="shared" si="30"/>
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="U43" s="13">
-        <v>3929</v>
+        <v>3934</v>
       </c>
       <c r="V43" s="5">
         <f t="shared" si="31"/>
-        <v>0.98992189468379943</v>
+        <v>0.99118165784832446</v>
       </c>
       <c r="W43" s="7">
         <v>4009</v>
@@ -8333,14 +8333,14 @@
       </c>
       <c r="Y43" s="4">
         <f t="shared" si="32"/>
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="Z43" s="13">
-        <v>3971</v>
+        <v>3975</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="33"/>
-        <v>0.99052132701421802</v>
+        <v>0.991519082065353</v>
       </c>
       <c r="AB43" s="7">
         <v>4962</v>
@@ -8350,14 +8350,14 @@
       </c>
       <c r="AD43" s="4">
         <f t="shared" si="34"/>
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="AE43" s="13">
-        <v>4926</v>
+        <v>4930</v>
       </c>
       <c r="AF43" s="5">
         <f t="shared" si="35"/>
-        <v>0.99274486094316805</v>
+        <v>0.99355098750503834</v>
       </c>
       <c r="AG43" s="7">
         <v>4018</v>
@@ -8367,14 +8367,14 @@
       </c>
       <c r="AI43" s="4">
         <f t="shared" si="36"/>
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="AJ43" s="13">
-        <v>3999</v>
+        <v>4005</v>
       </c>
       <c r="AK43" s="5">
         <f t="shared" si="37"/>
-        <v>0.99527127924340464</v>
+        <v>0.99676455948232956</v>
       </c>
       <c r="AL43" s="7">
         <v>4086</v>
@@ -8384,14 +8384,14 @@
       </c>
       <c r="AN43" s="4">
         <f t="shared" si="38"/>
-        <v>1184</v>
+        <v>1191</v>
       </c>
       <c r="AO43" s="13">
-        <v>4056</v>
+        <v>4063</v>
       </c>
       <c r="AP43" s="5">
         <f t="shared" si="39"/>
-        <v>0.9926578560939795</v>
+        <v>0.99437102300538427</v>
       </c>
       <c r="AQ43" s="7">
         <v>5072</v>
@@ -8401,14 +8401,14 @@
       </c>
       <c r="AS43" s="4">
         <f t="shared" si="40"/>
-        <v>1540</v>
+        <v>1559</v>
       </c>
       <c r="AT43" s="13">
-        <v>5053</v>
+        <v>5072</v>
       </c>
       <c r="AU43" s="5">
         <f t="shared" si="41"/>
-        <v>0.99625394321766558</v>
+        <v>1</v>
       </c>
       <c r="AV43" s="7">
         <v>4151</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="AX43" s="4">
         <f t="shared" si="42"/>
-        <v>1247</v>
+        <v>1267</v>
       </c>
       <c r="AY43" s="13">
-        <v>4088</v>
+        <v>4108</v>
       </c>
       <c r="AZ43" s="5">
         <f t="shared" si="43"/>
-        <v>0.98482293423271505</v>
+        <v>0.98964105034931338</v>
       </c>
       <c r="BA43" s="7">
         <v>4249</v>
@@ -8435,14 +8435,14 @@
       </c>
       <c r="BC43" s="4">
         <f t="shared" si="44"/>
-        <v>1149</v>
+        <v>1187</v>
       </c>
       <c r="BD43" s="13">
-        <v>4120</v>
+        <v>4158</v>
       </c>
       <c r="BE43" s="5">
         <f t="shared" si="45"/>
-        <v>0.96963991527418214</v>
+        <v>0.97858319604612853</v>
       </c>
       <c r="BF43" s="7">
         <v>5295</v>
@@ -8452,14 +8452,14 @@
       </c>
       <c r="BH43" s="4">
         <f t="shared" si="46"/>
-        <v>1682</v>
+        <v>1788</v>
       </c>
       <c r="BI43" s="6">
-        <v>4981</v>
+        <v>5087</v>
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="47"/>
-        <v>0.94069877242681776</v>
+        <v>0.96071765816808308</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8477,14 +8477,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="24"/>
-        <v>84201</v>
+        <v>84230</v>
       </c>
       <c r="F44" s="13">
-        <v>379620</v>
+        <v>379649</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="25"/>
-        <v>0.98978458457832075</v>
+        <v>0.98986019638210554</v>
       </c>
       <c r="H44" s="7">
         <v>388149</v>
@@ -8494,14 +8494,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="26"/>
-        <v>82507</v>
+        <v>82550</v>
       </c>
       <c r="K44" s="13">
-        <v>382925</v>
+        <v>382968</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="27"/>
-        <v>0.98654125091137679</v>
+        <v>0.98665203311099603</v>
       </c>
       <c r="M44" s="7">
         <v>456953</v>
@@ -8511,14 +8511,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="28"/>
-        <v>103428</v>
+        <v>103482</v>
       </c>
       <c r="P44" s="13">
-        <v>453040</v>
+        <v>453094</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="29"/>
-        <v>0.9914367560777585</v>
+        <v>0.99155493015693075</v>
       </c>
       <c r="R44" s="7">
         <v>388846</v>
@@ -8528,14 +8528,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="30"/>
-        <v>83466</v>
+        <v>83527</v>
       </c>
       <c r="U44" s="13">
-        <v>385253</v>
+        <v>385314</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="31"/>
-        <v>0.99075983808500023</v>
+        <v>0.99091671252886748</v>
       </c>
       <c r="W44" s="7">
         <v>393146</v>
@@ -8545,14 +8545,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="32"/>
-        <v>82059</v>
+        <v>82140</v>
       </c>
       <c r="Z44" s="13">
-        <v>387767</v>
+        <v>387848</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="33"/>
-        <v>0.98631805995736954</v>
+        <v>0.98652409028706889</v>
       </c>
       <c r="AB44" s="7">
         <v>465292</v>
@@ -8562,14 +8562,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="34"/>
-        <v>81703</v>
+        <v>81851</v>
       </c>
       <c r="AE44" s="13">
-        <v>460095</v>
+        <v>460243</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="35"/>
-        <v>0.98883066977295975</v>
+        <v>0.98914874960240018</v>
       </c>
       <c r="AG44" s="7">
         <v>393778</v>
@@ -8579,14 +8579,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="36"/>
-        <v>80284</v>
+        <v>80443</v>
       </c>
       <c r="AJ44" s="13">
-        <v>391490</v>
+        <v>391649</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="37"/>
-        <v>0.99418961953181739</v>
+        <v>0.99459340034232491</v>
       </c>
       <c r="AL44" s="7">
         <v>398873</v>
@@ -8596,14 +8596,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="38"/>
-        <v>77490</v>
+        <v>77736</v>
       </c>
       <c r="AO44" s="13">
-        <v>401015</v>
+        <v>401261</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="39"/>
-        <v>1.0053701303422393</v>
+        <v>1.0059868680005917</v>
       </c>
       <c r="AQ44" s="7">
         <v>476819</v>
@@ -8613,14 +8613,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="40"/>
-        <v>86214</v>
+        <v>86715</v>
       </c>
       <c r="AT44" s="13">
-        <v>477648</v>
+        <v>478149</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="41"/>
-        <v>1.0017386052149768</v>
+        <v>1.002789318378672</v>
       </c>
       <c r="AV44" s="7">
         <v>408878</v>
@@ -8630,14 +8630,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="42"/>
-        <v>73605</v>
+        <v>74283</v>
       </c>
       <c r="AY44" s="13">
-        <v>408983</v>
+        <v>409661</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="43"/>
-        <v>1.000256800316965</v>
+        <v>1.0019149966493672</v>
       </c>
       <c r="BA44" s="7">
         <v>416024</v>
@@ -8647,14 +8647,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="44"/>
-        <v>80932</v>
+        <v>82107</v>
       </c>
       <c r="BD44" s="13">
-        <v>413617</v>
+        <v>414792</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="45"/>
-        <v>0.99421427609945578</v>
+        <v>0.99703863238659307</v>
       </c>
       <c r="BF44" s="7">
         <v>493955</v>
@@ -8664,14 +8664,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="46"/>
-        <v>104863</v>
+        <v>107929</v>
       </c>
       <c r="BI44" s="6">
-        <v>485449</v>
+        <v>488515</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="47"/>
-        <v>0.98277980787723573</v>
+        <v>0.98898685102893991</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8689,14 +8689,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="24"/>
-        <v>56008</v>
+        <v>56032</v>
       </c>
       <c r="F45" s="13">
-        <v>276966</v>
+        <v>276990</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="25"/>
-        <v>0.99809006255946031</v>
+        <v>0.99817655029261687</v>
       </c>
       <c r="H45" s="7">
         <v>280269</v>
@@ -8706,14 +8706,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="26"/>
-        <v>55553</v>
+        <v>55583</v>
       </c>
       <c r="K45" s="13">
-        <v>278690</v>
+        <v>278720</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="27"/>
-        <v>0.9943661268281544</v>
+        <v>0.99447316685041875</v>
       </c>
       <c r="M45" s="7">
         <v>334005</v>
@@ -8723,14 +8723,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="28"/>
-        <v>70189</v>
+        <v>70241</v>
       </c>
       <c r="P45" s="13">
-        <v>331699</v>
+        <v>331751</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="29"/>
-        <v>0.99309591173784828</v>
+        <v>0.99325159802996965</v>
       </c>
       <c r="R45" s="7">
         <v>281510</v>
@@ -8740,14 +8740,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="30"/>
-        <v>53746</v>
+        <v>53796</v>
       </c>
       <c r="U45" s="13">
-        <v>279807</v>
+        <v>279857</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="31"/>
-        <v>0.99395048133281239</v>
+        <v>0.99412809491669918</v>
       </c>
       <c r="W45" s="7">
         <v>284325</v>
@@ -8757,14 +8757,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="32"/>
-        <v>54509</v>
+        <v>54581</v>
       </c>
       <c r="Z45" s="13">
-        <v>280834</v>
+        <v>280906</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="33"/>
-        <v>0.98772179723907505</v>
+        <v>0.98797502857645303</v>
       </c>
       <c r="AB45" s="7">
         <v>338696</v>
@@ -8774,14 +8774,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="34"/>
-        <v>61443</v>
+        <v>61555</v>
       </c>
       <c r="AE45" s="13">
-        <v>334635</v>
+        <v>334747</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="35"/>
-        <v>0.98800989678059381</v>
+        <v>0.98834057680043463</v>
       </c>
       <c r="AG45" s="7">
         <v>285325</v>
@@ -8791,14 +8791,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="36"/>
-        <v>56714</v>
+        <v>56826</v>
       </c>
       <c r="AJ45" s="13">
-        <v>282669</v>
+        <v>282781</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="37"/>
-        <v>0.99069131691930257</v>
+        <v>0.99108385174800662</v>
       </c>
       <c r="AL45" s="7">
         <v>289428</v>
@@ -8808,14 +8808,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="38"/>
-        <v>53209</v>
+        <v>53396</v>
       </c>
       <c r="AO45" s="13">
-        <v>289330</v>
+        <v>289517</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="39"/>
-        <v>0.99966140110839308</v>
+        <v>1.0003075030750308</v>
       </c>
       <c r="AQ45" s="7">
         <v>348161</v>
@@ -8825,14 +8825,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="40"/>
-        <v>66434</v>
+        <v>66868</v>
       </c>
       <c r="AT45" s="13">
-        <v>346728</v>
+        <v>347162</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="41"/>
-        <v>0.99588408810866236</v>
+        <v>0.99713063783709266</v>
       </c>
       <c r="AV45" s="7">
         <v>296165</v>
@@ -8842,14 +8842,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="42"/>
-        <v>52411</v>
+        <v>52920</v>
       </c>
       <c r="AY45" s="13">
-        <v>294444</v>
+        <v>294953</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="43"/>
-        <v>0.99418905002279134</v>
+        <v>0.99590768659362183</v>
       </c>
       <c r="BA45" s="7">
         <v>300603</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="44"/>
-        <v>58139</v>
+        <v>59017</v>
       </c>
       <c r="BD45" s="13">
-        <v>297622</v>
+        <v>298500</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="45"/>
-        <v>0.99008326596873619</v>
+        <v>0.99300406183571022</v>
       </c>
       <c r="BF45" s="7">
         <v>359430</v>
@@ -8876,14 +8876,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="46"/>
-        <v>78445</v>
+        <v>80728</v>
       </c>
       <c r="BI45" s="6">
-        <v>352352</v>
+        <v>354635</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="47"/>
-        <v>0.98030770942881784</v>
+        <v>0.9866594329911248</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8901,14 +8901,14 @@
       </c>
       <c r="E46" s="4">
         <f t="shared" si="24"/>
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F46" s="13">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" si="25"/>
-        <v>1.0329218106995885</v>
+        <v>1.0333333333333334</v>
       </c>
       <c r="H46" s="7">
         <v>2594</v>
@@ -8918,14 +8918,14 @@
       </c>
       <c r="J46" s="4">
         <f t="shared" si="26"/>
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="K46" s="13">
-        <v>2652</v>
+        <v>2653</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="27"/>
-        <v>1.0223592906707788</v>
+        <v>1.0227447956823439</v>
       </c>
       <c r="M46" s="7">
         <v>8454</v>
@@ -8935,14 +8935,14 @@
       </c>
       <c r="O46" s="4">
         <f t="shared" si="28"/>
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="P46" s="13">
-        <v>8599</v>
+        <v>8604</v>
       </c>
       <c r="Q46" s="5">
         <f t="shared" si="29"/>
-        <v>1.0171516441920985</v>
+        <v>1.0177430801987224</v>
       </c>
       <c r="R46" s="7">
         <v>2484</v>
@@ -8952,14 +8952,14 @@
       </c>
       <c r="T46" s="4">
         <f t="shared" si="30"/>
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="U46" s="13">
-        <v>2601</v>
+        <v>2605</v>
       </c>
       <c r="V46" s="5">
         <f t="shared" si="31"/>
-        <v>1.0471014492753623</v>
+        <v>1.0487117552334944</v>
       </c>
       <c r="W46" s="7">
         <v>2748</v>
@@ -8969,14 +8969,14 @@
       </c>
       <c r="Y46" s="4">
         <f t="shared" si="32"/>
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="Z46" s="13">
-        <v>2701</v>
+        <v>2704</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="33"/>
-        <v>0.98289665211062593</v>
+        <v>0.98398835516739447</v>
       </c>
       <c r="AB46" s="7">
         <v>8770</v>
@@ -8986,14 +8986,14 @@
       </c>
       <c r="AD46" s="4">
         <f t="shared" si="34"/>
-        <v>2088</v>
+        <v>2098</v>
       </c>
       <c r="AE46" s="13">
-        <v>8831</v>
+        <v>8841</v>
       </c>
       <c r="AF46" s="5">
         <f t="shared" si="35"/>
-        <v>1.0069555302166477</v>
+        <v>1.0080957810718358</v>
       </c>
       <c r="AG46" s="7">
         <v>2523</v>
@@ -9003,14 +9003,14 @@
       </c>
       <c r="AI46" s="4">
         <f t="shared" si="36"/>
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="AJ46" s="13">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="AK46" s="5">
         <f t="shared" si="37"/>
-        <v>1.0170432025366627</v>
+        <v>1.0194213238208483</v>
       </c>
       <c r="AL46" s="7">
         <v>2722</v>
@@ -9020,14 +9020,14 @@
       </c>
       <c r="AN46" s="4">
         <f t="shared" si="38"/>
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="AO46" s="13">
-        <v>2695</v>
+        <v>2706</v>
       </c>
       <c r="AP46" s="5">
         <f t="shared" si="39"/>
-        <v>0.99008082292432031</v>
+        <v>0.99412196914033801</v>
       </c>
       <c r="AQ46" s="7">
         <v>8967</v>
@@ -9037,14 +9037,14 @@
       </c>
       <c r="AS46" s="4">
         <f t="shared" si="40"/>
-        <v>1731</v>
+        <v>1759</v>
       </c>
       <c r="AT46" s="13">
-        <v>8961</v>
+        <v>8989</v>
       </c>
       <c r="AU46" s="5">
         <f t="shared" si="41"/>
-        <v>0.99933087989294078</v>
+        <v>1.0024534403925505</v>
       </c>
       <c r="AV46" s="7">
         <v>2626</v>
@@ -9054,14 +9054,14 @@
       </c>
       <c r="AX46" s="4">
         <f t="shared" si="42"/>
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="AY46" s="13">
-        <v>2641</v>
+        <v>2660</v>
       </c>
       <c r="AZ46" s="5">
         <f t="shared" si="43"/>
-        <v>1.0057121096725057</v>
+        <v>1.012947448591013</v>
       </c>
       <c r="BA46" s="7">
         <v>2791</v>
@@ -9071,14 +9071,14 @@
       </c>
       <c r="BC46" s="4">
         <f t="shared" si="44"/>
-        <v>523</v>
+        <v>547</v>
       </c>
       <c r="BD46" s="13">
-        <v>2688</v>
+        <v>2712</v>
       </c>
       <c r="BE46" s="5">
         <f t="shared" si="45"/>
-        <v>0.96309566463633112</v>
+        <v>0.97169473307058407</v>
       </c>
       <c r="BF46" s="7">
         <v>9093</v>
@@ -9088,14 +9088,14 @@
       </c>
       <c r="BH46" s="4">
         <f t="shared" si="46"/>
-        <v>1721</v>
+        <v>1806</v>
       </c>
       <c r="BI46" s="6">
-        <v>8908</v>
+        <v>8993</v>
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="47"/>
-        <v>0.97965467942373252</v>
+        <v>0.98900252941823386</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9300,14 +9300,14 @@
       </c>
       <c r="BH47" s="20">
         <f t="shared" si="46"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BI47" s="6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="BJ47" s="21">
         <f t="shared" si="47"/>
-        <v>0.98611111111111116</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.3">
@@ -9325,15 +9325,15 @@
       </c>
       <c r="E48" s="11">
         <f t="shared" si="24"/>
-        <v>1591305</v>
+        <v>1592629</v>
       </c>
       <c r="F48" s="10">
         <f>SUM(F10:F47)</f>
-        <v>8593352</v>
+        <v>8594676</v>
       </c>
       <c r="G48" s="12">
         <f t="shared" si="25"/>
-        <v>0.99655204564863331</v>
+        <v>0.99670558700344336</v>
       </c>
       <c r="H48" s="9">
         <f>SUM(H10:H47)</f>
@@ -9345,15 +9345,15 @@
       </c>
       <c r="J48" s="11">
         <f t="shared" si="26"/>
-        <v>1553268</v>
+        <v>1554845</v>
       </c>
       <c r="K48" s="10">
         <f>SUM(K10:K47)</f>
-        <v>8702514</v>
+        <v>8704091</v>
       </c>
       <c r="L48" s="12">
         <f t="shared" si="27"/>
-        <v>0.99195212101876196</v>
+        <v>0.99213187465028119</v>
       </c>
       <c r="M48" s="9">
         <f>SUM(M10:M47)</f>
@@ -9365,15 +9365,15 @@
       </c>
       <c r="O48" s="11">
         <f t="shared" si="28"/>
-        <v>2525624</v>
+        <v>2528777</v>
       </c>
       <c r="P48" s="10">
         <f>SUM(P10:P47)</f>
-        <v>13295221</v>
+        <v>13298374</v>
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="29"/>
-        <v>0.99548724940176292</v>
+        <v>0.99572333207367669</v>
       </c>
       <c r="R48" s="9">
         <f>SUM(R10:R47)</f>
@@ -9385,15 +9385,15 @@
       </c>
       <c r="T48" s="11">
         <f t="shared" si="30"/>
-        <v>1560413</v>
+        <v>1562718</v>
       </c>
       <c r="U48" s="10">
         <f>SUM(U10:U47)</f>
-        <v>8738614</v>
+        <v>8740919</v>
       </c>
       <c r="V48" s="12">
         <f t="shared" si="31"/>
-        <v>0.99634827188249164</v>
+        <v>0.99661108046594538</v>
       </c>
       <c r="W48" s="9">
         <f>SUM(W10:W47)</f>
@@ -9405,15 +9405,15 @@
       </c>
       <c r="Y48" s="11">
         <f t="shared" si="32"/>
-        <v>1573062</v>
+        <v>1575888</v>
       </c>
       <c r="Z48" s="10">
         <f>SUM(Z10:Z47)</f>
-        <v>8829035</v>
+        <v>8831861</v>
       </c>
       <c r="AA48" s="12">
         <f t="shared" si="33"/>
-        <v>0.98840893883542846</v>
+        <v>0.98872530904589306</v>
       </c>
       <c r="AB48" s="9">
         <f>SUM(AB10:AB47)</f>
@@ -9425,15 +9425,15 @@
       </c>
       <c r="AD48" s="11">
         <f t="shared" si="34"/>
-        <v>2378865</v>
+        <v>2384884</v>
       </c>
       <c r="AE48" s="10">
         <f>SUM(AE10:AE47)</f>
-        <v>13515588</v>
+        <v>13521607</v>
       </c>
       <c r="AF48" s="12">
         <f t="shared" si="35"/>
-        <v>0.99322286245913194</v>
+        <v>0.99366518198005405</v>
       </c>
       <c r="AG48" s="9">
         <f>SUM(AG10:AG47)</f>
@@ -9445,15 +9445,15 @@
       </c>
       <c r="AI48" s="11">
         <f t="shared" si="36"/>
-        <v>1590177</v>
+        <v>1594839</v>
       </c>
       <c r="AJ48" s="10">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8875036</v>
+        <v>8879698</v>
       </c>
       <c r="AK48" s="12">
         <f t="shared" si="37"/>
-        <v>0.99528232484447865</v>
+        <v>0.99580514032358491</v>
       </c>
       <c r="AL48" s="9">
         <f>SUM(AL10:AL47)</f>
@@ -9465,15 +9465,15 @@
       </c>
       <c r="AN48" s="11">
         <f t="shared" si="38"/>
-        <v>1511203</v>
+        <v>1518010</v>
       </c>
       <c r="AO48" s="10">
         <f>SUM(AO10:AO47)</f>
-        <v>9135083</v>
+        <v>9141890</v>
       </c>
       <c r="AP48" s="12">
         <f t="shared" si="39"/>
-        <v>1.0008461373277706</v>
+        <v>1.0015919170493988</v>
       </c>
       <c r="AQ48" s="9">
         <f>SUM(AQ10:AQ47)</f>
@@ -9485,15 +9485,15 @@
       </c>
       <c r="AS48" s="11">
         <f t="shared" si="40"/>
-        <v>2324005</v>
+        <v>2341442</v>
       </c>
       <c r="AT48" s="10">
         <f>SUM(AT10:AT47)</f>
-        <v>13965066</v>
+        <v>13982503</v>
       </c>
       <c r="AU48" s="12">
         <f t="shared" si="41"/>
-        <v>0.99913723315774883</v>
+        <v>1.0003847715463658</v>
       </c>
       <c r="AV48" s="9">
         <f>SUM(AV10:AV47)</f>
@@ -9505,15 +9505,15 @@
       </c>
       <c r="AX48" s="11">
         <f t="shared" si="42"/>
-        <v>1447859</v>
+        <v>1465135</v>
       </c>
       <c r="AY48" s="10">
         <f>SUM(AY10:AY47)</f>
-        <v>9246921</v>
+        <v>9264197</v>
       </c>
       <c r="AZ48" s="12">
         <f t="shared" si="43"/>
-        <v>0.99960640229209863</v>
+        <v>1.0014739645007513</v>
       </c>
       <c r="BA48" s="9">
         <f>SUM(BA10:BA47)</f>
@@ -9525,15 +9525,15 @@
       </c>
       <c r="BC48" s="11">
         <f t="shared" si="44"/>
-        <v>1494805</v>
+        <v>1522617</v>
       </c>
       <c r="BD48" s="10">
         <f>SUM(BD10:BD47)</f>
-        <v>9386007</v>
+        <v>9413819</v>
       </c>
       <c r="BE48" s="12">
         <f t="shared" si="45"/>
-        <v>0.99105684318115705</v>
+        <v>0.99399347778227698</v>
       </c>
       <c r="BF48" s="9">
         <f>SUM(BF10:BF47)</f>
@@ -9545,18 +9545,18 @@
       </c>
       <c r="BH48" s="11">
         <f t="shared" si="46"/>
-        <v>2755040</v>
+        <v>2843385</v>
       </c>
       <c r="BI48" s="10">
         <f>SUM(BI10:BI47)</f>
-        <v>14160011</v>
+        <v>14248356</v>
       </c>
       <c r="BJ48" s="12">
         <f t="shared" si="47"/>
-        <v>0.98124941920266207</v>
+        <v>0.98737148223915672</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -9589,8 +9589,38 @@
       <c r="AD50" s="1"/>
       <c r="AE50" s="1"/>
       <c r="AF50" s="1"/>
+      <c r="AG50" s="1"/>
+      <c r="AH50" s="1"/>
+      <c r="AI50" s="1"/>
+      <c r="AJ50" s="1"/>
+      <c r="AK50" s="1"/>
+      <c r="AL50" s="1"/>
+      <c r="AM50" s="1"/>
+      <c r="AN50" s="1"/>
+      <c r="AO50" s="1"/>
+      <c r="AP50" s="1"/>
+      <c r="AQ50" s="1"/>
+      <c r="AR50" s="1"/>
+      <c r="AS50" s="1"/>
+      <c r="AT50" s="1"/>
+      <c r="AU50" s="1"/>
+      <c r="AV50" s="1"/>
+      <c r="AW50" s="1"/>
+      <c r="AX50" s="1"/>
+      <c r="AY50" s="1"/>
+      <c r="AZ50" s="1"/>
+      <c r="BA50" s="1"/>
+      <c r="BB50" s="1"/>
+      <c r="BC50" s="1"/>
+      <c r="BD50" s="1"/>
+      <c r="BE50" s="1"/>
+      <c r="BF50" s="1"/>
+      <c r="BG50" s="1"/>
+      <c r="BH50" s="1"/>
+      <c r="BI50" s="1"/>
+      <c r="BJ50" s="1"/>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -9624,7 +9654,7 @@
       <c r="AE51" s="1"/>
       <c r="AF51" s="1"/>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -9658,7 +9688,7 @@
       <c r="AE52" s="1"/>
       <c r="AF52" s="1"/>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -9692,7 +9722,7 @@
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A54" s="19" t="s">
         <v>45</v>
       </c>
@@ -9728,7 +9758,7 @@
       <c r="AE54" s="1"/>
       <c r="AF54" s="1"/>
     </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:62" x14ac:dyDescent="0.3">
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -9758,7 +9788,7 @@
       <c r="AE55" s="1"/>
       <c r="AF55" s="1"/>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:62" x14ac:dyDescent="0.3">
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -9788,7 +9818,7 @@
       <c r="AE56" s="1"/>
       <c r="AF56" s="1"/>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:62" x14ac:dyDescent="0.3">
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
